--- a/胎壓偵測/PORSCHE_Data.xlsx
+++ b/胎壓偵測/PORSCHE_Data.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J602"/>
+  <dimension ref="A1:J678"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7523,26 +7523,10 @@
           <t>AMI</t>
         </is>
       </c>
-      <c r="G143" t="inlineStr">
-        <is>
-          <t>05/2019 - 04/2024</t>
-        </is>
-      </c>
-      <c r="H143" t="inlineStr">
-        <is>
-          <t>RDE047 + RDV021 | 45.142.000, RDE047 + RDV026 | 73.907.047</t>
-        </is>
-      </c>
-      <c r="I143" t="inlineStr">
-        <is>
-          <t>BH SENS</t>
-        </is>
-      </c>
-      <c r="J143" t="inlineStr">
-        <is>
-          <t>433</t>
-        </is>
-      </c>
+      <c r="G143" t="inlineStr"/>
+      <c r="H143" t="inlineStr"/>
+      <c r="I143" t="inlineStr"/>
+      <c r="J143" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -28866,7 +28850,7 @@
       </c>
       <c r="D578" t="inlineStr">
         <is>
-          <t>2013-01 ~ 2016-01</t>
+          <t>2011-01 ~ 2013-01</t>
         </is>
       </c>
       <c r="E578" t="inlineStr">
@@ -28876,17 +28860,17 @@
       </c>
       <c r="F578" t="inlineStr">
         <is>
-          <t>AGR</t>
+          <t>ADR</t>
         </is>
       </c>
       <c r="G578" t="inlineStr">
         <is>
-          <t>04/2013 -, 09/2009 - 12/2013</t>
+          <t>09/2009 - 12/2013</t>
         </is>
       </c>
       <c r="H578" t="inlineStr">
         <is>
-          <t>RDE047 + RDV021 | 45.142.000, RDE047 + RDV026 | 73.907.047, RDE048 + RDV021 | 45.144.000</t>
+          <t>RDE048 + RDV021 | 45.144.000</t>
         </is>
       </c>
       <c r="I578" t="inlineStr">
@@ -28913,12 +28897,12 @@
       </c>
       <c r="C579" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3.6</t>
         </is>
       </c>
       <c r="D579" t="inlineStr">
         <is>
-          <t>2013-01 ~ 2016-01</t>
+          <t>2011-01 ~ 2013-01</t>
         </is>
       </c>
       <c r="E579" t="inlineStr">
@@ -28928,17 +28912,17 @@
       </c>
       <c r="F579" t="inlineStr">
         <is>
-          <t>AGM</t>
+          <t>AEH</t>
         </is>
       </c>
       <c r="G579" t="inlineStr">
         <is>
-          <t>04/2013 -, 09/2009 - 12/2013</t>
+          <t>09/2009 - 12/2013</t>
         </is>
       </c>
       <c r="H579" t="inlineStr">
         <is>
-          <t>RDE047 + RDV021 | 45.142.000, RDE047 + RDV026 | 73.907.047, RDE048 + RDV021 | 45.144.000</t>
+          <t>RDE048 + RDV021 | 45.144.000</t>
         </is>
       </c>
       <c r="I579" t="inlineStr">
@@ -28965,12 +28949,12 @@
       </c>
       <c r="C580" t="inlineStr">
         <is>
-          <t>4 E-Hybrid</t>
+          <t>3.6</t>
         </is>
       </c>
       <c r="D580" t="inlineStr">
         <is>
-          <t>2024-01 ~ 至今</t>
+          <t>2013-01 ~ 2016-01</t>
         </is>
       </c>
       <c r="E580" t="inlineStr">
@@ -28980,17 +28964,17 @@
       </c>
       <c r="F580" t="inlineStr">
         <is>
-          <t>AOB</t>
+          <t>AGR</t>
         </is>
       </c>
       <c r="G580" t="inlineStr">
         <is>
-          <t>06/2023 - 04/2030</t>
+          <t>04/2013 -, 09/2009 - 12/2013</t>
         </is>
       </c>
       <c r="H580" t="inlineStr">
         <is>
-          <t>RDE047 + RDV021 | 45.142.000, RDE047 + RDV026 | 73.907.047, RDE254+RDV021, RDE254+RDV026</t>
+          <t>RDE047 + RDV021 | 45.142.000, RDE047 + RDV026 | 73.907.047, RDE048 + RDV021 | 45.144.000</t>
         </is>
       </c>
       <c r="I580" t="inlineStr">
@@ -29017,12 +29001,12 @@
       </c>
       <c r="C581" t="inlineStr">
         <is>
-          <t>4.0 GTS</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D581" t="inlineStr">
         <is>
-          <t>2020-01 ~ 2023-01</t>
+          <t>2013-01 ~ 2016-01</t>
         </is>
       </c>
       <c r="E581" t="inlineStr">
@@ -29032,17 +29016,17 @@
       </c>
       <c r="F581" t="inlineStr">
         <is>
-          <t>AMR</t>
+          <t>AGM</t>
         </is>
       </c>
       <c r="G581" t="inlineStr">
         <is>
-          <t>04/2013 -</t>
+          <t>04/2013 -, 09/2009 - 12/2013</t>
         </is>
       </c>
       <c r="H581" t="inlineStr">
         <is>
-          <t>RDE047 + RDV021 | 45.142.000, RDE047 + RDV026 | 73.907.047</t>
+          <t>RDE047 + RDV021 | 45.142.000, RDE047 + RDV026 | 73.907.047, RDE048 + RDV021 | 45.144.000</t>
         </is>
       </c>
       <c r="I581" t="inlineStr">
@@ -29069,12 +29053,12 @@
       </c>
       <c r="C582" t="inlineStr">
         <is>
-          <t>4.0 Turbo S</t>
+          <t>4 3.6</t>
         </is>
       </c>
       <c r="D582" t="inlineStr">
         <is>
-          <t>2020-01 ~ 2023-01</t>
+          <t>2011-01 ~ 2013-01</t>
         </is>
       </c>
       <c r="E582" t="inlineStr">
@@ -29084,17 +29068,17 @@
       </c>
       <c r="F582" t="inlineStr">
         <is>
-          <t>AMT</t>
+          <t>ADS</t>
         </is>
       </c>
       <c r="G582" t="inlineStr">
         <is>
-          <t>04/2013 -</t>
+          <t>09/2009 - 12/2013</t>
         </is>
       </c>
       <c r="H582" t="inlineStr">
         <is>
-          <t>RDE047 + RDV021 | 45.142.000, RDE047 + RDV026 | 73.907.047</t>
+          <t>RDE048 + RDV021 | 45.144.000</t>
         </is>
       </c>
       <c r="I582" t="inlineStr">
@@ -29121,12 +29105,12 @@
       </c>
       <c r="C583" t="inlineStr">
         <is>
-          <t>4.0 Turbo S E-Hybrid</t>
+          <t>4 3.6</t>
         </is>
       </c>
       <c r="D583" t="inlineStr">
         <is>
-          <t>2017-01 ~ 2020-01</t>
+          <t>2011-01 ~ 2013-01</t>
         </is>
       </c>
       <c r="E583" t="inlineStr">
@@ -29136,17 +29120,17 @@
       </c>
       <c r="F583" t="inlineStr">
         <is>
-          <t>AKC</t>
+          <t>AEI</t>
         </is>
       </c>
       <c r="G583" t="inlineStr">
         <is>
-          <t>04/2013 -</t>
+          <t>09/2009 - 12/2013</t>
         </is>
       </c>
       <c r="H583" t="inlineStr">
         <is>
-          <t>RDE047 + RDV021 | 45.142.000, RDE047 + RDV026 | 73.907.047</t>
+          <t>RDE048 + RDV021 | 45.144.000</t>
         </is>
       </c>
       <c r="I583" t="inlineStr">
@@ -29173,12 +29157,12 @@
       </c>
       <c r="C584" t="inlineStr">
         <is>
-          <t>4.0 Turbo S E-Hybrid</t>
+          <t>4 E-Hybrid</t>
         </is>
       </c>
       <c r="D584" t="inlineStr">
         <is>
-          <t>2020-01 ~ 2023-01</t>
+          <t>2024-01 ~ 至今</t>
         </is>
       </c>
       <c r="E584" t="inlineStr">
@@ -29188,17 +29172,17 @@
       </c>
       <c r="F584" t="inlineStr">
         <is>
-          <t>AMV</t>
+          <t>AOB</t>
         </is>
       </c>
       <c r="G584" t="inlineStr">
         <is>
-          <t>04/2013 -</t>
+          <t>06/2023 - 04/2030</t>
         </is>
       </c>
       <c r="H584" t="inlineStr">
         <is>
-          <t>RDE047 + RDV021 | 45.142.000, RDE047 + RDV026 | 73.907.047</t>
+          <t>RDE047 + RDV021 | 45.142.000, RDE047 + RDV026 | 73.907.047, RDE254+RDV021, RDE254+RDV026</t>
         </is>
       </c>
       <c r="I584" t="inlineStr">
@@ -29225,12 +29209,12 @@
       </c>
       <c r="C585" t="inlineStr">
         <is>
-          <t>4S</t>
+          <t>4.0 GTS</t>
         </is>
       </c>
       <c r="D585" t="inlineStr">
         <is>
-          <t>2013-01 ~ 2016-01</t>
+          <t>2020-01 ~ 2023-01</t>
         </is>
       </c>
       <c r="E585" t="inlineStr">
@@ -29240,17 +29224,17 @@
       </c>
       <c r="F585" t="inlineStr">
         <is>
-          <t>AGO</t>
+          <t>AMR</t>
         </is>
       </c>
       <c r="G585" t="inlineStr">
         <is>
-          <t>04/2013 -, 09/2009 - 12/2013</t>
+          <t>04/2013 -</t>
         </is>
       </c>
       <c r="H585" t="inlineStr">
         <is>
-          <t>RDE047 + RDV021 | 45.142.000, RDE047 + RDV026 | 73.907.047, RDE048 + RDV021 | 45.144.000</t>
+          <t>RDE047 + RDV021 | 45.142.000, RDE047 + RDV026 | 73.907.047</t>
         </is>
       </c>
       <c r="I585" t="inlineStr">
@@ -29277,12 +29261,12 @@
       </c>
       <c r="C586" t="inlineStr">
         <is>
-          <t>4S</t>
+          <t>4.0 Turbo S</t>
         </is>
       </c>
       <c r="D586" t="inlineStr">
         <is>
-          <t>2016-01 ~ 2020-01</t>
+          <t>2020-01 ~ 2023-01</t>
         </is>
       </c>
       <c r="E586" t="inlineStr">
@@ -29292,7 +29276,7 @@
       </c>
       <c r="F586" t="inlineStr">
         <is>
-          <t>AJP</t>
+          <t>AMT</t>
         </is>
       </c>
       <c r="G586" t="inlineStr">
@@ -29329,12 +29313,12 @@
       </c>
       <c r="C587" t="inlineStr">
         <is>
-          <t>4S</t>
+          <t>4.0 Turbo S E-Hybrid</t>
         </is>
       </c>
       <c r="D587" t="inlineStr">
         <is>
-          <t>2020-01 ~ 2023-01</t>
+          <t>2017-01 ~ 2020-01</t>
         </is>
       </c>
       <c r="E587" t="inlineStr">
@@ -29344,7 +29328,7 @@
       </c>
       <c r="F587" t="inlineStr">
         <is>
-          <t>AJP</t>
+          <t>AKC</t>
         </is>
       </c>
       <c r="G587" t="inlineStr">
@@ -29381,12 +29365,12 @@
       </c>
       <c r="C588" t="inlineStr">
         <is>
-          <t>4S Diesel</t>
+          <t>4.0 Turbo S E-Hybrid</t>
         </is>
       </c>
       <c r="D588" t="inlineStr">
         <is>
-          <t>2016-01 ~ 2020-01</t>
+          <t>2020-01 ~ 2023-01</t>
         </is>
       </c>
       <c r="E588" t="inlineStr">
@@ -29396,7 +29380,7 @@
       </c>
       <c r="F588" t="inlineStr">
         <is>
-          <t>AJQ</t>
+          <t>AMV</t>
         </is>
       </c>
       <c r="G588" t="inlineStr">
@@ -29433,12 +29417,12 @@
       </c>
       <c r="C589" t="inlineStr">
         <is>
-          <t>4S E-Hybrid</t>
+          <t>4S</t>
         </is>
       </c>
       <c r="D589" t="inlineStr">
         <is>
-          <t>2024-01 ~ 至今</t>
+          <t>2009-01 ~ 2013-01</t>
         </is>
       </c>
       <c r="E589" t="inlineStr">
@@ -29448,17 +29432,17 @@
       </c>
       <c r="F589" t="inlineStr">
         <is>
-          <t>AOC</t>
+          <t>ACR</t>
         </is>
       </c>
       <c r="G589" t="inlineStr">
         <is>
-          <t>06/2023 - 04/2030</t>
+          <t>09/2009 - 12/2013</t>
         </is>
       </c>
       <c r="H589" t="inlineStr">
         <is>
-          <t>RDE047 + RDV021 | 45.142.000, RDE047 + RDV026 | 73.907.047, RDE254+RDV021, RDE254+RDV026</t>
+          <t>RDE048 + RDV021 | 45.144.000</t>
         </is>
       </c>
       <c r="I589" t="inlineStr">
@@ -29485,12 +29469,12 @@
       </c>
       <c r="C590" t="inlineStr">
         <is>
-          <t>Diesel</t>
+          <t>4S</t>
         </is>
       </c>
       <c r="D590" t="inlineStr">
         <is>
-          <t>2013-01 ~ 2016-01</t>
+          <t>2009-01 ~ 2013-01</t>
         </is>
       </c>
       <c r="E590" t="inlineStr">
@@ -29500,17 +29484,17 @@
       </c>
       <c r="F590" t="inlineStr">
         <is>
-          <t>AEV</t>
+          <t>AEK</t>
         </is>
       </c>
       <c r="G590" t="inlineStr">
         <is>
-          <t>04/2013 -, 09/2009 - 12/2013</t>
+          <t>09/2009 - 12/2013</t>
         </is>
       </c>
       <c r="H590" t="inlineStr">
         <is>
-          <t>RDE047 + RDV021 | 45.142.000, RDE047 + RDV026 | 73.907.047, RDE048 + RDV021 | 45.144.000</t>
+          <t>RDE048 + RDV021 | 45.144.000</t>
         </is>
       </c>
       <c r="I590" t="inlineStr">
@@ -29537,7 +29521,7 @@
       </c>
       <c r="C591" t="inlineStr">
         <is>
-          <t>Diesel</t>
+          <t>4S</t>
         </is>
       </c>
       <c r="D591" t="inlineStr">
@@ -29552,7 +29536,7 @@
       </c>
       <c r="F591" t="inlineStr">
         <is>
-          <t>AEW</t>
+          <t>AGO</t>
         </is>
       </c>
       <c r="G591" t="inlineStr">
@@ -29589,12 +29573,12 @@
       </c>
       <c r="C592" t="inlineStr">
         <is>
-          <t>Diesel</t>
+          <t>4S</t>
         </is>
       </c>
       <c r="D592" t="inlineStr">
         <is>
-          <t>2013-01 ~ 2016-01</t>
+          <t>2016-01 ~ 2020-01</t>
         </is>
       </c>
       <c r="E592" t="inlineStr">
@@ -29604,17 +29588,17 @@
       </c>
       <c r="F592" t="inlineStr">
         <is>
-          <t>AGW</t>
+          <t>AJP</t>
         </is>
       </c>
       <c r="G592" t="inlineStr">
         <is>
-          <t>04/2013 -, 09/2009 - 12/2013</t>
+          <t>04/2013 -</t>
         </is>
       </c>
       <c r="H592" t="inlineStr">
         <is>
-          <t>RDE047 + RDV021 | 45.142.000, RDE047 + RDV026 | 73.907.047, RDE048 + RDV021 | 45.144.000</t>
+          <t>RDE047 + RDV021 | 45.142.000, RDE047 + RDV026 | 73.907.047</t>
         </is>
       </c>
       <c r="I592" t="inlineStr">
@@ -29641,12 +29625,12 @@
       </c>
       <c r="C593" t="inlineStr">
         <is>
-          <t>GTS</t>
+          <t>4S</t>
         </is>
       </c>
       <c r="D593" t="inlineStr">
         <is>
-          <t>2013-01 ~ 2016-01</t>
+          <t>2020-01 ~ 2023-01</t>
         </is>
       </c>
       <c r="E593" t="inlineStr">
@@ -29656,17 +29640,17 @@
       </c>
       <c r="F593" t="inlineStr">
         <is>
-          <t>AFI</t>
+          <t>AJP</t>
         </is>
       </c>
       <c r="G593" t="inlineStr">
         <is>
-          <t>04/2013 -, 09/2009 - 12/2013</t>
+          <t>04/2013 -</t>
         </is>
       </c>
       <c r="H593" t="inlineStr">
         <is>
-          <t>RDE047 + RDV021 | 45.142.000, RDE047 + RDV026 | 73.907.047, RDE048 + RDV021 | 45.144.000</t>
+          <t>RDE047 + RDV021 | 45.142.000, RDE047 + RDV026 | 73.907.047</t>
         </is>
       </c>
       <c r="I593" t="inlineStr">
@@ -29693,12 +29677,12 @@
       </c>
       <c r="C594" t="inlineStr">
         <is>
-          <t>GTS</t>
+          <t>4S Diesel</t>
         </is>
       </c>
       <c r="D594" t="inlineStr">
         <is>
-          <t>2013-01 ~ 2016-01</t>
+          <t>2016-01 ~ 2020-01</t>
         </is>
       </c>
       <c r="E594" t="inlineStr">
@@ -29708,17 +29692,17 @@
       </c>
       <c r="F594" t="inlineStr">
         <is>
-          <t>AGQ</t>
+          <t>AJQ</t>
         </is>
       </c>
       <c r="G594" t="inlineStr">
         <is>
-          <t>04/2013 -, 09/2009 - 12/2013</t>
+          <t>04/2013 -</t>
         </is>
       </c>
       <c r="H594" t="inlineStr">
         <is>
-          <t>RDE047 + RDV021 | 45.142.000, RDE047 + RDV026 | 73.907.047, RDE048 + RDV021 | 45.144.000</t>
+          <t>RDE047 + RDV021 | 45.142.000, RDE047 + RDV026 | 73.907.047</t>
         </is>
       </c>
       <c r="I594" t="inlineStr">
@@ -29745,12 +29729,12 @@
       </c>
       <c r="C595" t="inlineStr">
         <is>
-          <t>GTS</t>
+          <t>4S E-Hybrid</t>
         </is>
       </c>
       <c r="D595" t="inlineStr">
         <is>
-          <t>2019-01 ~ 2020-01</t>
+          <t>2024-01 ~ 至今</t>
         </is>
       </c>
       <c r="E595" t="inlineStr">
@@ -29760,17 +29744,17 @@
       </c>
       <c r="F595" t="inlineStr">
         <is>
-          <t>ALA</t>
+          <t>AOC</t>
         </is>
       </c>
       <c r="G595" t="inlineStr">
         <is>
-          <t>04/2013 -</t>
+          <t>06/2023 - 04/2030</t>
         </is>
       </c>
       <c r="H595" t="inlineStr">
         <is>
-          <t>RDE047 + RDV021 | 45.142.000, RDE047 + RDV026 | 73.907.047</t>
+          <t>RDE047 + RDV021 | 45.142.000, RDE047 + RDV026 | 73.907.047, RDE254+RDV021, RDE254+RDV026</t>
         </is>
       </c>
       <c r="I595" t="inlineStr">
@@ -29797,12 +29781,12 @@
       </c>
       <c r="C596" t="inlineStr">
         <is>
-          <t>GTS</t>
+          <t>Diesel</t>
         </is>
       </c>
       <c r="D596" t="inlineStr">
         <is>
-          <t>2024-01 ~ 至今</t>
+          <t>2009-01 ~ 2013-01</t>
         </is>
       </c>
       <c r="E596" t="inlineStr">
@@ -29812,17 +29796,17 @@
       </c>
       <c r="F596" t="inlineStr">
         <is>
-          <t>AOD</t>
+          <t>AEW</t>
         </is>
       </c>
       <c r="G596" t="inlineStr">
         <is>
-          <t>06/2023 - 04/2030</t>
+          <t>09/2009 - 12/2013</t>
         </is>
       </c>
       <c r="H596" t="inlineStr">
         <is>
-          <t>RDE047 + RDV021 | 45.142.000, RDE047 + RDV026 | 73.907.047, RDE254+RDV021, RDE254+RDV026</t>
+          <t>RDE048 + RDV021 | 45.144.000</t>
         </is>
       </c>
       <c r="I596" t="inlineStr">
@@ -29849,12 +29833,12 @@
       </c>
       <c r="C597" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>Diesel</t>
         </is>
       </c>
       <c r="D597" t="inlineStr">
         <is>
-          <t>2013-01 ~ 2016-01</t>
+          <t>2009-01 ~ 2013-01</t>
         </is>
       </c>
       <c r="E597" t="inlineStr">
@@ -29864,17 +29848,17 @@
       </c>
       <c r="F597" t="inlineStr">
         <is>
-          <t>AGN</t>
+          <t>AFD</t>
         </is>
       </c>
       <c r="G597" t="inlineStr">
         <is>
-          <t>04/2013 -, 09/2009 - 12/2013</t>
+          <t>09/2009 - 12/2013</t>
         </is>
       </c>
       <c r="H597" t="inlineStr">
         <is>
-          <t>RDE047 + RDV021 | 45.142.000, RDE047 + RDV026 | 73.907.047, RDE048 + RDV021 | 45.144.000</t>
+          <t>RDE048 + RDV021 | 45.144.000</t>
         </is>
       </c>
       <c r="I597" t="inlineStr">
@@ -29901,12 +29885,12 @@
       </c>
       <c r="C598" t="inlineStr">
         <is>
-          <t>S E-Hybrid</t>
+          <t>Diesel</t>
         </is>
       </c>
       <c r="D598" t="inlineStr">
         <is>
-          <t>2013-01 ~ 2016-01</t>
+          <t>2011-01 ~ 2013-01</t>
         </is>
       </c>
       <c r="E598" t="inlineStr">
@@ -29916,17 +29900,17 @@
       </c>
       <c r="F598" t="inlineStr">
         <is>
-          <t>AGL</t>
+          <t>AEV</t>
         </is>
       </c>
       <c r="G598" t="inlineStr">
         <is>
-          <t>04/2013 -, 09/2009 - 12/2013</t>
+          <t>09/2009 - 12/2013</t>
         </is>
       </c>
       <c r="H598" t="inlineStr">
         <is>
-          <t>RDE047 + RDV021 | 45.142.000, RDE047 + RDV026 | 73.907.047, RDE048 + RDV021 | 45.144.000</t>
+          <t>RDE048 + RDV021 | 45.144.000</t>
         </is>
       </c>
       <c r="I598" t="inlineStr">
@@ -29953,12 +29937,12 @@
       </c>
       <c r="C599" t="inlineStr">
         <is>
-          <t>Turbo</t>
+          <t>Diesel</t>
         </is>
       </c>
       <c r="D599" t="inlineStr">
         <is>
-          <t>2013-01 ~ 2016-01</t>
+          <t>2011-01 ~ 2013-01</t>
         </is>
       </c>
       <c r="E599" t="inlineStr">
@@ -29968,17 +29952,17 @@
       </c>
       <c r="F599" t="inlineStr">
         <is>
-          <t>AGP</t>
+          <t>AFC</t>
         </is>
       </c>
       <c r="G599" t="inlineStr">
         <is>
-          <t>04/2013 -, 09/2009 - 12/2013</t>
+          <t>09/2009 - 12/2013</t>
         </is>
       </c>
       <c r="H599" t="inlineStr">
         <is>
-          <t>RDE047 + RDV021 | 45.142.000, RDE047 + RDV026 | 73.907.047, RDE048 + RDV021 | 45.144.000</t>
+          <t>RDE048 + RDV021 | 45.144.000</t>
         </is>
       </c>
       <c r="I599" t="inlineStr">
@@ -30005,12 +29989,12 @@
       </c>
       <c r="C600" t="inlineStr">
         <is>
-          <t>Turbo</t>
+          <t>Diesel</t>
         </is>
       </c>
       <c r="D600" t="inlineStr">
         <is>
-          <t>2016-01 ~ 2020-01</t>
+          <t>2013-01 ~ 2016-01</t>
         </is>
       </c>
       <c r="E600" t="inlineStr">
@@ -30020,17 +30004,17 @@
       </c>
       <c r="F600" t="inlineStr">
         <is>
-          <t>AJR</t>
+          <t>AEV</t>
         </is>
       </c>
       <c r="G600" t="inlineStr">
         <is>
-          <t>04/2013 -</t>
+          <t>04/2013 -, 09/2009 - 12/2013</t>
         </is>
       </c>
       <c r="H600" t="inlineStr">
         <is>
-          <t>RDE047 + RDV021 | 45.142.000, RDE047 + RDV026 | 73.907.047</t>
+          <t>RDE047 + RDV021 | 45.142.000, RDE047 + RDV026 | 73.907.047, RDE048 + RDV021 | 45.144.000</t>
         </is>
       </c>
       <c r="I600" t="inlineStr">
@@ -30057,12 +30041,12 @@
       </c>
       <c r="C601" t="inlineStr">
         <is>
-          <t>Turbo E-Hybrid</t>
+          <t>Diesel</t>
         </is>
       </c>
       <c r="D601" t="inlineStr">
         <is>
-          <t>2024-01 ~ 至今</t>
+          <t>2013-01 ~ 2016-01</t>
         </is>
       </c>
       <c r="E601" t="inlineStr">
@@ -30072,17 +30056,17 @@
       </c>
       <c r="F601" t="inlineStr">
         <is>
-          <t>AOF</t>
+          <t>AEW</t>
         </is>
       </c>
       <c r="G601" t="inlineStr">
         <is>
-          <t>06/2023 - 04/2030</t>
+          <t>04/2013 -, 09/2009 - 12/2013</t>
         </is>
       </c>
       <c r="H601" t="inlineStr">
         <is>
-          <t>RDE047 + RDV021 | 45.142.000, RDE047 + RDV026 | 73.907.047, RDE254+RDV021, RDE254+RDV026</t>
+          <t>RDE047 + RDV021 | 45.142.000, RDE047 + RDV026 | 73.907.047, RDE048 + RDV021 | 45.144.000</t>
         </is>
       </c>
       <c r="I601" t="inlineStr">
@@ -30109,40 +30093,3992 @@
       </c>
       <c r="C602" t="inlineStr">
         <is>
+          <t>Diesel</t>
+        </is>
+      </c>
+      <c r="D602" t="inlineStr">
+        <is>
+          <t>2013-01 ~ 2016-01</t>
+        </is>
+      </c>
+      <c r="E602" t="inlineStr">
+        <is>
+          <t>0583</t>
+        </is>
+      </c>
+      <c r="F602" t="inlineStr">
+        <is>
+          <t>AGW</t>
+        </is>
+      </c>
+      <c r="G602" t="inlineStr">
+        <is>
+          <t>04/2013 -, 09/2009 - 12/2013</t>
+        </is>
+      </c>
+      <c r="H602" t="inlineStr">
+        <is>
+          <t>RDE047 + RDV021 | 45.142.000, RDE047 + RDV026 | 73.907.047, RDE048 + RDV021 | 45.144.000</t>
+        </is>
+      </c>
+      <c r="I602" t="inlineStr">
+        <is>
+          <t>BH SENS</t>
+        </is>
+      </c>
+      <c r="J602" t="inlineStr">
+        <is>
+          <t>433</t>
+        </is>
+      </c>
+    </row>
+    <row r="603">
+      <c r="A603" t="inlineStr">
+        <is>
+          <t>PORSCHE</t>
+        </is>
+      </c>
+      <c r="B603" t="inlineStr">
+        <is>
+          <t>Panamera</t>
+        </is>
+      </c>
+      <c r="C603" t="inlineStr">
+        <is>
+          <t>GTS</t>
+        </is>
+      </c>
+      <c r="D603" t="inlineStr">
+        <is>
+          <t>2011-01 ~ 2013-01</t>
+        </is>
+      </c>
+      <c r="E603" t="inlineStr">
+        <is>
+          <t>0583</t>
+        </is>
+      </c>
+      <c r="F603" t="inlineStr">
+        <is>
+          <t>AFI</t>
+        </is>
+      </c>
+      <c r="G603" t="inlineStr">
+        <is>
+          <t>09/2009 - 12/2013</t>
+        </is>
+      </c>
+      <c r="H603" t="inlineStr">
+        <is>
+          <t>RDE048 + RDV021 | 45.144.000</t>
+        </is>
+      </c>
+      <c r="I603" t="inlineStr">
+        <is>
+          <t>BH SENS</t>
+        </is>
+      </c>
+      <c r="J603" t="inlineStr">
+        <is>
+          <t>433</t>
+        </is>
+      </c>
+    </row>
+    <row r="604">
+      <c r="A604" t="inlineStr">
+        <is>
+          <t>PORSCHE</t>
+        </is>
+      </c>
+      <c r="B604" t="inlineStr">
+        <is>
+          <t>Panamera</t>
+        </is>
+      </c>
+      <c r="C604" t="inlineStr">
+        <is>
+          <t>GTS</t>
+        </is>
+      </c>
+      <c r="D604" t="inlineStr">
+        <is>
+          <t>2011-01 ~ 2013-01</t>
+        </is>
+      </c>
+      <c r="E604" t="inlineStr">
+        <is>
+          <t>0583</t>
+        </is>
+      </c>
+      <c r="F604" t="inlineStr">
+        <is>
+          <t>AFJ</t>
+        </is>
+      </c>
+      <c r="G604" t="inlineStr">
+        <is>
+          <t>09/2009 - 12/2013</t>
+        </is>
+      </c>
+      <c r="H604" t="inlineStr">
+        <is>
+          <t>RDE048 + RDV021 | 45.144.000</t>
+        </is>
+      </c>
+      <c r="I604" t="inlineStr">
+        <is>
+          <t>BH SENS</t>
+        </is>
+      </c>
+      <c r="J604" t="inlineStr">
+        <is>
+          <t>433</t>
+        </is>
+      </c>
+    </row>
+    <row r="605">
+      <c r="A605" t="inlineStr">
+        <is>
+          <t>PORSCHE</t>
+        </is>
+      </c>
+      <c r="B605" t="inlineStr">
+        <is>
+          <t>Panamera</t>
+        </is>
+      </c>
+      <c r="C605" t="inlineStr">
+        <is>
+          <t>GTS</t>
+        </is>
+      </c>
+      <c r="D605" t="inlineStr">
+        <is>
+          <t>2013-01 ~ 2016-01</t>
+        </is>
+      </c>
+      <c r="E605" t="inlineStr">
+        <is>
+          <t>0583</t>
+        </is>
+      </c>
+      <c r="F605" t="inlineStr">
+        <is>
+          <t>AFI</t>
+        </is>
+      </c>
+      <c r="G605" t="inlineStr">
+        <is>
+          <t>04/2013 -, 09/2009 - 12/2013</t>
+        </is>
+      </c>
+      <c r="H605" t="inlineStr">
+        <is>
+          <t>RDE047 + RDV021 | 45.142.000, RDE047 + RDV026 | 73.907.047, RDE048 + RDV021 | 45.144.000</t>
+        </is>
+      </c>
+      <c r="I605" t="inlineStr">
+        <is>
+          <t>BH SENS</t>
+        </is>
+      </c>
+      <c r="J605" t="inlineStr">
+        <is>
+          <t>433</t>
+        </is>
+      </c>
+    </row>
+    <row r="606">
+      <c r="A606" t="inlineStr">
+        <is>
+          <t>PORSCHE</t>
+        </is>
+      </c>
+      <c r="B606" t="inlineStr">
+        <is>
+          <t>Panamera</t>
+        </is>
+      </c>
+      <c r="C606" t="inlineStr">
+        <is>
+          <t>GTS</t>
+        </is>
+      </c>
+      <c r="D606" t="inlineStr">
+        <is>
+          <t>2013-01 ~ 2016-01</t>
+        </is>
+      </c>
+      <c r="E606" t="inlineStr">
+        <is>
+          <t>0583</t>
+        </is>
+      </c>
+      <c r="F606" t="inlineStr">
+        <is>
+          <t>AGQ</t>
+        </is>
+      </c>
+      <c r="G606" t="inlineStr">
+        <is>
+          <t>04/2013 -, 09/2009 - 12/2013</t>
+        </is>
+      </c>
+      <c r="H606" t="inlineStr">
+        <is>
+          <t>RDE047 + RDV021 | 45.142.000, RDE047 + RDV026 | 73.907.047, RDE048 + RDV021 | 45.144.000</t>
+        </is>
+      </c>
+      <c r="I606" t="inlineStr">
+        <is>
+          <t>BH SENS</t>
+        </is>
+      </c>
+      <c r="J606" t="inlineStr">
+        <is>
+          <t>433</t>
+        </is>
+      </c>
+    </row>
+    <row r="607">
+      <c r="A607" t="inlineStr">
+        <is>
+          <t>PORSCHE</t>
+        </is>
+      </c>
+      <c r="B607" t="inlineStr">
+        <is>
+          <t>Panamera</t>
+        </is>
+      </c>
+      <c r="C607" t="inlineStr">
+        <is>
+          <t>GTS</t>
+        </is>
+      </c>
+      <c r="D607" t="inlineStr">
+        <is>
+          <t>2019-01 ~ 2020-01</t>
+        </is>
+      </c>
+      <c r="E607" t="inlineStr">
+        <is>
+          <t>0583</t>
+        </is>
+      </c>
+      <c r="F607" t="inlineStr">
+        <is>
+          <t>ALA</t>
+        </is>
+      </c>
+      <c r="G607" t="inlineStr">
+        <is>
+          <t>04/2013 -</t>
+        </is>
+      </c>
+      <c r="H607" t="inlineStr">
+        <is>
+          <t>RDE047 + RDV021 | 45.142.000, RDE047 + RDV026 | 73.907.047</t>
+        </is>
+      </c>
+      <c r="I607" t="inlineStr">
+        <is>
+          <t>BH SENS</t>
+        </is>
+      </c>
+      <c r="J607" t="inlineStr">
+        <is>
+          <t>433</t>
+        </is>
+      </c>
+    </row>
+    <row r="608">
+      <c r="A608" t="inlineStr">
+        <is>
+          <t>PORSCHE</t>
+        </is>
+      </c>
+      <c r="B608" t="inlineStr">
+        <is>
+          <t>Panamera</t>
+        </is>
+      </c>
+      <c r="C608" t="inlineStr">
+        <is>
+          <t>GTS</t>
+        </is>
+      </c>
+      <c r="D608" t="inlineStr">
+        <is>
+          <t>2024-01 ~ 至今</t>
+        </is>
+      </c>
+      <c r="E608" t="inlineStr">
+        <is>
+          <t>0583</t>
+        </is>
+      </c>
+      <c r="F608" t="inlineStr">
+        <is>
+          <t>AOD</t>
+        </is>
+      </c>
+      <c r="G608" t="inlineStr">
+        <is>
+          <t>06/2023 - 04/2030</t>
+        </is>
+      </c>
+      <c r="H608" t="inlineStr">
+        <is>
+          <t>RDE047 + RDV021 | 45.142.000, RDE047 + RDV026 | 73.907.047, RDE254+RDV021, RDE254+RDV026</t>
+        </is>
+      </c>
+      <c r="I608" t="inlineStr">
+        <is>
+          <t>BH SENS</t>
+        </is>
+      </c>
+      <c r="J608" t="inlineStr">
+        <is>
+          <t>433</t>
+        </is>
+      </c>
+    </row>
+    <row r="609">
+      <c r="A609" t="inlineStr">
+        <is>
+          <t>PORSCHE</t>
+        </is>
+      </c>
+      <c r="B609" t="inlineStr">
+        <is>
+          <t>Panamera</t>
+        </is>
+      </c>
+      <c r="C609" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="D609" t="inlineStr">
+        <is>
+          <t>2009-01 ~ 2013-01</t>
+        </is>
+      </c>
+      <c r="E609" t="inlineStr">
+        <is>
+          <t>0583</t>
+        </is>
+      </c>
+      <c r="F609" t="inlineStr">
+        <is>
+          <t>ACQ</t>
+        </is>
+      </c>
+      <c r="G609" t="inlineStr">
+        <is>
+          <t>09/2009 - 12/2013</t>
+        </is>
+      </c>
+      <c r="H609" t="inlineStr">
+        <is>
+          <t>RDE048 + RDV021 | 45.144.000</t>
+        </is>
+      </c>
+      <c r="I609" t="inlineStr">
+        <is>
+          <t>BH SENS</t>
+        </is>
+      </c>
+      <c r="J609" t="inlineStr">
+        <is>
+          <t>433</t>
+        </is>
+      </c>
+    </row>
+    <row r="610">
+      <c r="A610" t="inlineStr">
+        <is>
+          <t>PORSCHE</t>
+        </is>
+      </c>
+      <c r="B610" t="inlineStr">
+        <is>
+          <t>Panamera</t>
+        </is>
+      </c>
+      <c r="C610" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="D610" t="inlineStr">
+        <is>
+          <t>2009-01 ~ 2013-01</t>
+        </is>
+      </c>
+      <c r="E610" t="inlineStr">
+        <is>
+          <t>0583</t>
+        </is>
+      </c>
+      <c r="F610" t="inlineStr">
+        <is>
+          <t>AEJ</t>
+        </is>
+      </c>
+      <c r="G610" t="inlineStr">
+        <is>
+          <t>09/2009 - 12/2013</t>
+        </is>
+      </c>
+      <c r="H610" t="inlineStr">
+        <is>
+          <t>RDE048 + RDV021 | 45.144.000</t>
+        </is>
+      </c>
+      <c r="I610" t="inlineStr">
+        <is>
+          <t>BH SENS</t>
+        </is>
+      </c>
+      <c r="J610" t="inlineStr">
+        <is>
+          <t>433</t>
+        </is>
+      </c>
+    </row>
+    <row r="611">
+      <c r="A611" t="inlineStr">
+        <is>
+          <t>PORSCHE</t>
+        </is>
+      </c>
+      <c r="B611" t="inlineStr">
+        <is>
+          <t>Panamera</t>
+        </is>
+      </c>
+      <c r="C611" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="D611" t="inlineStr">
+        <is>
+          <t>2013-01 ~ 2016-01</t>
+        </is>
+      </c>
+      <c r="E611" t="inlineStr">
+        <is>
+          <t>0583</t>
+        </is>
+      </c>
+      <c r="F611" t="inlineStr">
+        <is>
+          <t>AGN</t>
+        </is>
+      </c>
+      <c r="G611" t="inlineStr">
+        <is>
+          <t>04/2013 -, 09/2009 - 12/2013</t>
+        </is>
+      </c>
+      <c r="H611" t="inlineStr">
+        <is>
+          <t>RDE047 + RDV021 | 45.142.000, RDE047 + RDV026 | 73.907.047, RDE048 + RDV021 | 45.144.000</t>
+        </is>
+      </c>
+      <c r="I611" t="inlineStr">
+        <is>
+          <t>BH SENS</t>
+        </is>
+      </c>
+      <c r="J611" t="inlineStr">
+        <is>
+          <t>433</t>
+        </is>
+      </c>
+    </row>
+    <row r="612">
+      <c r="A612" t="inlineStr">
+        <is>
+          <t>PORSCHE</t>
+        </is>
+      </c>
+      <c r="B612" t="inlineStr">
+        <is>
+          <t>Panamera</t>
+        </is>
+      </c>
+      <c r="C612" t="inlineStr">
+        <is>
+          <t>S E-Hybrid</t>
+        </is>
+      </c>
+      <c r="D612" t="inlineStr">
+        <is>
+          <t>2013-01 ~ 2016-01</t>
+        </is>
+      </c>
+      <c r="E612" t="inlineStr">
+        <is>
+          <t>0583</t>
+        </is>
+      </c>
+      <c r="F612" t="inlineStr">
+        <is>
+          <t>AGL</t>
+        </is>
+      </c>
+      <c r="G612" t="inlineStr">
+        <is>
+          <t>04/2013 -, 09/2009 - 12/2013</t>
+        </is>
+      </c>
+      <c r="H612" t="inlineStr">
+        <is>
+          <t>RDE047 + RDV021 | 45.142.000, RDE047 + RDV026 | 73.907.047, RDE048 + RDV021 | 45.144.000</t>
+        </is>
+      </c>
+      <c r="I612" t="inlineStr">
+        <is>
+          <t>BH SENS</t>
+        </is>
+      </c>
+      <c r="J612" t="inlineStr">
+        <is>
+          <t>433</t>
+        </is>
+      </c>
+    </row>
+    <row r="613">
+      <c r="A613" t="inlineStr">
+        <is>
+          <t>PORSCHE</t>
+        </is>
+      </c>
+      <c r="B613" t="inlineStr">
+        <is>
+          <t>Panamera</t>
+        </is>
+      </c>
+      <c r="C613" t="inlineStr">
+        <is>
+          <t>S Hybrid</t>
+        </is>
+      </c>
+      <c r="D613" t="inlineStr">
+        <is>
+          <t>2011-01 ~ 2013-01</t>
+        </is>
+      </c>
+      <c r="E613" t="inlineStr">
+        <is>
+          <t>0583</t>
+        </is>
+      </c>
+      <c r="F613" t="inlineStr">
+        <is>
+          <t>AEU</t>
+        </is>
+      </c>
+      <c r="G613" t="inlineStr">
+        <is>
+          <t>09/2009 - 12/2013</t>
+        </is>
+      </c>
+      <c r="H613" t="inlineStr">
+        <is>
+          <t>RDE048 + RDV021 | 45.144.000</t>
+        </is>
+      </c>
+      <c r="I613" t="inlineStr">
+        <is>
+          <t>BH SENS</t>
+        </is>
+      </c>
+      <c r="J613" t="inlineStr">
+        <is>
+          <t>433</t>
+        </is>
+      </c>
+    </row>
+    <row r="614">
+      <c r="A614" t="inlineStr">
+        <is>
+          <t>PORSCHE</t>
+        </is>
+      </c>
+      <c r="B614" t="inlineStr">
+        <is>
+          <t>Panamera</t>
+        </is>
+      </c>
+      <c r="C614" t="inlineStr">
+        <is>
+          <t>S Hybrid</t>
+        </is>
+      </c>
+      <c r="D614" t="inlineStr">
+        <is>
+          <t>2011-01 ~ 2013-01</t>
+        </is>
+      </c>
+      <c r="E614" t="inlineStr">
+        <is>
+          <t>0583</t>
+        </is>
+      </c>
+      <c r="F614" t="inlineStr">
+        <is>
+          <t>AFB</t>
+        </is>
+      </c>
+      <c r="G614" t="inlineStr">
+        <is>
+          <t>09/2009 - 12/2013</t>
+        </is>
+      </c>
+      <c r="H614" t="inlineStr">
+        <is>
+          <t>RDE048 + RDV021 | 45.144.000</t>
+        </is>
+      </c>
+      <c r="I614" t="inlineStr">
+        <is>
+          <t>BH SENS</t>
+        </is>
+      </c>
+      <c r="J614" t="inlineStr">
+        <is>
+          <t>433</t>
+        </is>
+      </c>
+    </row>
+    <row r="615">
+      <c r="A615" t="inlineStr">
+        <is>
+          <t>PORSCHE</t>
+        </is>
+      </c>
+      <c r="B615" t="inlineStr">
+        <is>
+          <t>Panamera</t>
+        </is>
+      </c>
+      <c r="C615" t="inlineStr">
+        <is>
+          <t>Turbo</t>
+        </is>
+      </c>
+      <c r="D615" t="inlineStr">
+        <is>
+          <t>2009-01 ~ 2013-01</t>
+        </is>
+      </c>
+      <c r="E615" t="inlineStr">
+        <is>
+          <t>0583</t>
+        </is>
+      </c>
+      <c r="F615" t="inlineStr">
+        <is>
+          <t>ACS</t>
+        </is>
+      </c>
+      <c r="G615" t="inlineStr">
+        <is>
+          <t>09/2009 - 12/2013</t>
+        </is>
+      </c>
+      <c r="H615" t="inlineStr">
+        <is>
+          <t>RDE048 + RDV021 | 45.144.000</t>
+        </is>
+      </c>
+      <c r="I615" t="inlineStr">
+        <is>
+          <t>BH SENS</t>
+        </is>
+      </c>
+      <c r="J615" t="inlineStr">
+        <is>
+          <t>433</t>
+        </is>
+      </c>
+    </row>
+    <row r="616">
+      <c r="A616" t="inlineStr">
+        <is>
+          <t>PORSCHE</t>
+        </is>
+      </c>
+      <c r="B616" t="inlineStr">
+        <is>
+          <t>Panamera</t>
+        </is>
+      </c>
+      <c r="C616" t="inlineStr">
+        <is>
+          <t>Turbo</t>
+        </is>
+      </c>
+      <c r="D616" t="inlineStr">
+        <is>
+          <t>2009-01 ~ 2013-01</t>
+        </is>
+      </c>
+      <c r="E616" t="inlineStr">
+        <is>
+          <t>0583</t>
+        </is>
+      </c>
+      <c r="F616" t="inlineStr">
+        <is>
+          <t>AEL</t>
+        </is>
+      </c>
+      <c r="G616" t="inlineStr">
+        <is>
+          <t>09/2009 - 12/2013</t>
+        </is>
+      </c>
+      <c r="H616" t="inlineStr">
+        <is>
+          <t>RDE048 + RDV021 | 45.144.000</t>
+        </is>
+      </c>
+      <c r="I616" t="inlineStr">
+        <is>
+          <t>BH SENS</t>
+        </is>
+      </c>
+      <c r="J616" t="inlineStr">
+        <is>
+          <t>433</t>
+        </is>
+      </c>
+    </row>
+    <row r="617">
+      <c r="A617" t="inlineStr">
+        <is>
+          <t>PORSCHE</t>
+        </is>
+      </c>
+      <c r="B617" t="inlineStr">
+        <is>
+          <t>Panamera</t>
+        </is>
+      </c>
+      <c r="C617" t="inlineStr">
+        <is>
+          <t>Turbo</t>
+        </is>
+      </c>
+      <c r="D617" t="inlineStr">
+        <is>
+          <t>2009-01 ~ 2013-01</t>
+        </is>
+      </c>
+      <c r="E617" t="inlineStr">
+        <is>
+          <t>0583</t>
+        </is>
+      </c>
+      <c r="F617" t="inlineStr">
+        <is>
+          <t>AEM</t>
+        </is>
+      </c>
+      <c r="G617" t="inlineStr">
+        <is>
+          <t>09/2009 - 12/2013</t>
+        </is>
+      </c>
+      <c r="H617" t="inlineStr">
+        <is>
+          <t>RDE048 + RDV021 | 45.144.000</t>
+        </is>
+      </c>
+      <c r="I617" t="inlineStr">
+        <is>
+          <t>BH SENS</t>
+        </is>
+      </c>
+      <c r="J617" t="inlineStr">
+        <is>
+          <t>433</t>
+        </is>
+      </c>
+    </row>
+    <row r="618">
+      <c r="A618" t="inlineStr">
+        <is>
+          <t>PORSCHE</t>
+        </is>
+      </c>
+      <c r="B618" t="inlineStr">
+        <is>
+          <t>Panamera</t>
+        </is>
+      </c>
+      <c r="C618" t="inlineStr">
+        <is>
+          <t>Turbo</t>
+        </is>
+      </c>
+      <c r="D618" t="inlineStr">
+        <is>
+          <t>2010-01 ~ 2013-01</t>
+        </is>
+      </c>
+      <c r="E618" t="inlineStr">
+        <is>
+          <t>0583</t>
+        </is>
+      </c>
+      <c r="F618" t="inlineStr">
+        <is>
+          <t>AED</t>
+        </is>
+      </c>
+      <c r="G618" t="inlineStr">
+        <is>
+          <t>09/2009 - 12/2013</t>
+        </is>
+      </c>
+      <c r="H618" t="inlineStr">
+        <is>
+          <t>RDE048 + RDV021 | 45.144.000</t>
+        </is>
+      </c>
+      <c r="I618" t="inlineStr">
+        <is>
+          <t>BH SENS</t>
+        </is>
+      </c>
+      <c r="J618" t="inlineStr">
+        <is>
+          <t>433</t>
+        </is>
+      </c>
+    </row>
+    <row r="619">
+      <c r="A619" t="inlineStr">
+        <is>
+          <t>PORSCHE</t>
+        </is>
+      </c>
+      <c r="B619" t="inlineStr">
+        <is>
+          <t>Panamera</t>
+        </is>
+      </c>
+      <c r="C619" t="inlineStr">
+        <is>
+          <t>Turbo</t>
+        </is>
+      </c>
+      <c r="D619" t="inlineStr">
+        <is>
+          <t>2013-01 ~ 2016-01</t>
+        </is>
+      </c>
+      <c r="E619" t="inlineStr">
+        <is>
+          <t>0583</t>
+        </is>
+      </c>
+      <c r="F619" t="inlineStr">
+        <is>
+          <t>AGP</t>
+        </is>
+      </c>
+      <c r="G619" t="inlineStr">
+        <is>
+          <t>04/2013 -, 09/2009 - 12/2013</t>
+        </is>
+      </c>
+      <c r="H619" t="inlineStr">
+        <is>
+          <t>RDE047 + RDV021 | 45.142.000, RDE047 + RDV026 | 73.907.047, RDE048 + RDV021 | 45.144.000</t>
+        </is>
+      </c>
+      <c r="I619" t="inlineStr">
+        <is>
+          <t>BH SENS</t>
+        </is>
+      </c>
+      <c r="J619" t="inlineStr">
+        <is>
+          <t>433</t>
+        </is>
+      </c>
+    </row>
+    <row r="620">
+      <c r="A620" t="inlineStr">
+        <is>
+          <t>PORSCHE</t>
+        </is>
+      </c>
+      <c r="B620" t="inlineStr">
+        <is>
+          <t>Panamera</t>
+        </is>
+      </c>
+      <c r="C620" t="inlineStr">
+        <is>
+          <t>Turbo</t>
+        </is>
+      </c>
+      <c r="D620" t="inlineStr">
+        <is>
+          <t>2016-01 ~ 2020-01</t>
+        </is>
+      </c>
+      <c r="E620" t="inlineStr">
+        <is>
+          <t>0583</t>
+        </is>
+      </c>
+      <c r="F620" t="inlineStr">
+        <is>
+          <t>AJR</t>
+        </is>
+      </c>
+      <c r="G620" t="inlineStr">
+        <is>
+          <t>04/2013 -</t>
+        </is>
+      </c>
+      <c r="H620" t="inlineStr">
+        <is>
+          <t>RDE047 + RDV021 | 45.142.000, RDE047 + RDV026 | 73.907.047</t>
+        </is>
+      </c>
+      <c r="I620" t="inlineStr">
+        <is>
+          <t>BH SENS</t>
+        </is>
+      </c>
+      <c r="J620" t="inlineStr">
+        <is>
+          <t>433</t>
+        </is>
+      </c>
+    </row>
+    <row r="621">
+      <c r="A621" t="inlineStr">
+        <is>
+          <t>PORSCHE</t>
+        </is>
+      </c>
+      <c r="B621" t="inlineStr">
+        <is>
+          <t>Panamera</t>
+        </is>
+      </c>
+      <c r="C621" t="inlineStr">
+        <is>
+          <t>Turbo E-Hybrid</t>
+        </is>
+      </c>
+      <c r="D621" t="inlineStr">
+        <is>
+          <t>2024-01 ~ 至今</t>
+        </is>
+      </c>
+      <c r="E621" t="inlineStr">
+        <is>
+          <t>0583</t>
+        </is>
+      </c>
+      <c r="F621" t="inlineStr">
+        <is>
+          <t>AOF</t>
+        </is>
+      </c>
+      <c r="G621" t="inlineStr">
+        <is>
+          <t>06/2023 - 04/2030</t>
+        </is>
+      </c>
+      <c r="H621" t="inlineStr">
+        <is>
+          <t>RDE047 + RDV021 | 45.142.000, RDE047 + RDV026 | 73.907.047, RDE254+RDV021, RDE254+RDV026</t>
+        </is>
+      </c>
+      <c r="I621" t="inlineStr">
+        <is>
+          <t>BH SENS</t>
+        </is>
+      </c>
+      <c r="J621" t="inlineStr">
+        <is>
+          <t>433</t>
+        </is>
+      </c>
+    </row>
+    <row r="622">
+      <c r="A622" t="inlineStr">
+        <is>
+          <t>PORSCHE</t>
+        </is>
+      </c>
+      <c r="B622" t="inlineStr">
+        <is>
+          <t>Panamera</t>
+        </is>
+      </c>
+      <c r="C622" t="inlineStr">
+        <is>
+          <t>Turbo S</t>
+        </is>
+      </c>
+      <c r="D622" t="inlineStr">
+        <is>
+          <t>2011-01 ~ 2013-01</t>
+        </is>
+      </c>
+      <c r="E622" t="inlineStr">
+        <is>
+          <t>0583</t>
+        </is>
+      </c>
+      <c r="F622" t="inlineStr">
+        <is>
+          <t>AEX</t>
+        </is>
+      </c>
+      <c r="G622" t="inlineStr">
+        <is>
+          <t>09/2009 - 12/2013</t>
+        </is>
+      </c>
+      <c r="H622" t="inlineStr">
+        <is>
+          <t>RDE048 + RDV021 | 45.144.000</t>
+        </is>
+      </c>
+      <c r="I622" t="inlineStr">
+        <is>
+          <t>BH SENS</t>
+        </is>
+      </c>
+      <c r="J622" t="inlineStr">
+        <is>
+          <t>433</t>
+        </is>
+      </c>
+    </row>
+    <row r="623">
+      <c r="A623" t="inlineStr">
+        <is>
+          <t>PORSCHE</t>
+        </is>
+      </c>
+      <c r="B623" t="inlineStr">
+        <is>
+          <t>Panamera</t>
+        </is>
+      </c>
+      <c r="C623" t="inlineStr">
+        <is>
+          <t>Turbo S</t>
+        </is>
+      </c>
+      <c r="D623" t="inlineStr">
+        <is>
+          <t>2011-01 ~ 2013-01</t>
+        </is>
+      </c>
+      <c r="E623" t="inlineStr">
+        <is>
+          <t>0583</t>
+        </is>
+      </c>
+      <c r="F623" t="inlineStr">
+        <is>
+          <t>AFA</t>
+        </is>
+      </c>
+      <c r="G623" t="inlineStr">
+        <is>
+          <t>09/2009 - 12/2013</t>
+        </is>
+      </c>
+      <c r="H623" t="inlineStr">
+        <is>
+          <t>RDE048 + RDV021 | 45.144.000</t>
+        </is>
+      </c>
+      <c r="I623" t="inlineStr">
+        <is>
+          <t>BH SENS</t>
+        </is>
+      </c>
+      <c r="J623" t="inlineStr">
+        <is>
+          <t>433</t>
+        </is>
+      </c>
+    </row>
+    <row r="624">
+      <c r="A624" t="inlineStr">
+        <is>
+          <t>PORSCHE</t>
+        </is>
+      </c>
+      <c r="B624" t="inlineStr">
+        <is>
+          <t>Panamera</t>
+        </is>
+      </c>
+      <c r="C624" t="inlineStr">
+        <is>
+          <t>Turbo S</t>
+        </is>
+      </c>
+      <c r="D624" t="inlineStr">
+        <is>
+          <t>2013-01 ~ 2016-01</t>
+        </is>
+      </c>
+      <c r="E624" t="inlineStr">
+        <is>
+          <t>0583</t>
+        </is>
+      </c>
+      <c r="F624" t="inlineStr">
+        <is>
+          <t>AGX</t>
+        </is>
+      </c>
+      <c r="G624" t="inlineStr">
+        <is>
+          <t>04/2013 -, 09/2009 - 12/2013</t>
+        </is>
+      </c>
+      <c r="H624" t="inlineStr">
+        <is>
+          <t>RDE047 + RDV021 | 45.142.000, RDE047 + RDV026 | 73.907.047, RDE048 + RDV021 | 45.144.000</t>
+        </is>
+      </c>
+      <c r="I624" t="inlineStr">
+        <is>
+          <t>BH SENS</t>
+        </is>
+      </c>
+      <c r="J624" t="inlineStr">
+        <is>
+          <t>433</t>
+        </is>
+      </c>
+    </row>
+    <row r="625">
+      <c r="A625" t="inlineStr">
+        <is>
+          <t>PORSCHE</t>
+        </is>
+      </c>
+      <c r="B625" t="inlineStr">
+        <is>
+          <t>Panamera</t>
+        </is>
+      </c>
+      <c r="C625" t="inlineStr">
+        <is>
           <t>Turbo S E-Hybrid</t>
         </is>
       </c>
-      <c r="D602" t="inlineStr">
+      <c r="D625" t="inlineStr">
         <is>
           <t>2024-01 ~ 至今</t>
         </is>
       </c>
-      <c r="E602" t="inlineStr">
-        <is>
-          <t>0583</t>
-        </is>
-      </c>
-      <c r="F602" t="inlineStr">
+      <c r="E625" t="inlineStr">
+        <is>
+          <t>0583</t>
+        </is>
+      </c>
+      <c r="F625" t="inlineStr">
         <is>
           <t>AOE</t>
         </is>
       </c>
-      <c r="G602" t="inlineStr">
+      <c r="G625" t="inlineStr">
         <is>
           <t>06/2023 - 04/2030</t>
         </is>
       </c>
-      <c r="H602" t="inlineStr">
+      <c r="H625" t="inlineStr">
         <is>
           <t>RDE047 + RDV021 | 45.142.000, RDE047 + RDV026 | 73.907.047, RDE254+RDV021, RDE254+RDV026</t>
         </is>
       </c>
-      <c r="I602" t="inlineStr">
-        <is>
-          <t>BH SENS</t>
-        </is>
-      </c>
-      <c r="J602" t="inlineStr">
+      <c r="I625" t="inlineStr">
+        <is>
+          <t>BH SENS</t>
+        </is>
+      </c>
+      <c r="J625" t="inlineStr">
+        <is>
+          <t>433</t>
+        </is>
+      </c>
+    </row>
+    <row r="626">
+      <c r="A626" t="inlineStr">
+        <is>
+          <t>PORSCHE</t>
+        </is>
+      </c>
+      <c r="B626" t="inlineStr">
+        <is>
+          <t>Panamera Sport Turismo</t>
+        </is>
+      </c>
+      <c r="C626" t="inlineStr">
+        <is>
+          <t>3.0 4</t>
+        </is>
+      </c>
+      <c r="D626" t="inlineStr">
+        <is>
+          <t>2017-01 ~ 2018-01</t>
+        </is>
+      </c>
+      <c r="E626" t="inlineStr">
+        <is>
+          <t>0583</t>
+        </is>
+      </c>
+      <c r="F626" t="inlineStr">
+        <is>
+          <t>AKE</t>
+        </is>
+      </c>
+      <c r="G626" t="inlineStr">
+        <is>
+          <t>04/2013 -</t>
+        </is>
+      </c>
+      <c r="H626" t="inlineStr">
+        <is>
+          <t>RDE047 + RDV021 | 45.142.000, RDE047 + RDV026 | 73.907.047</t>
+        </is>
+      </c>
+      <c r="I626" t="inlineStr">
+        <is>
+          <t>BH SENS</t>
+        </is>
+      </c>
+      <c r="J626" t="inlineStr">
+        <is>
+          <t>433</t>
+        </is>
+      </c>
+    </row>
+    <row r="627">
+      <c r="A627" t="inlineStr">
+        <is>
+          <t>PORSCHE</t>
+        </is>
+      </c>
+      <c r="B627" t="inlineStr">
+        <is>
+          <t>Panamera Sport Turismo</t>
+        </is>
+      </c>
+      <c r="C627" t="inlineStr">
+        <is>
+          <t>3.0 4</t>
+        </is>
+      </c>
+      <c r="D627" t="inlineStr">
+        <is>
+          <t>2019-01 ~ 2020-01</t>
+        </is>
+      </c>
+      <c r="E627" t="inlineStr">
+        <is>
+          <t>0583</t>
+        </is>
+      </c>
+      <c r="F627" t="inlineStr">
+        <is>
+          <t>ALD</t>
+        </is>
+      </c>
+      <c r="G627" t="inlineStr">
+        <is>
+          <t>04/2013 -</t>
+        </is>
+      </c>
+      <c r="H627" t="inlineStr">
+        <is>
+          <t>RDE047 + RDV021 | 45.142.000, RDE047 + RDV026 | 73.907.047</t>
+        </is>
+      </c>
+      <c r="I627" t="inlineStr">
+        <is>
+          <t>BH SENS</t>
+        </is>
+      </c>
+      <c r="J627" t="inlineStr">
+        <is>
+          <t>433</t>
+        </is>
+      </c>
+    </row>
+    <row r="628">
+      <c r="A628" t="inlineStr">
+        <is>
+          <t>PORSCHE</t>
+        </is>
+      </c>
+      <c r="B628" t="inlineStr">
+        <is>
+          <t>Panamera Sport Turismo</t>
+        </is>
+      </c>
+      <c r="C628" t="inlineStr">
+        <is>
+          <t>3.0 4</t>
+        </is>
+      </c>
+      <c r="D628" t="inlineStr">
+        <is>
+          <t>2020-01 ~ 2023-01</t>
+        </is>
+      </c>
+      <c r="E628" t="inlineStr">
+        <is>
+          <t>0583</t>
+        </is>
+      </c>
+      <c r="F628" t="inlineStr">
+        <is>
+          <t>ALD</t>
+        </is>
+      </c>
+      <c r="G628" t="inlineStr">
+        <is>
+          <t>04/2013 -</t>
+        </is>
+      </c>
+      <c r="H628" t="inlineStr">
+        <is>
+          <t>RDE047 + RDV021 | 45.142.000, RDE047 + RDV026 | 73.907.047</t>
+        </is>
+      </c>
+      <c r="I628" t="inlineStr">
+        <is>
+          <t>BH SENS</t>
+        </is>
+      </c>
+      <c r="J628" t="inlineStr">
+        <is>
+          <t>433</t>
+        </is>
+      </c>
+    </row>
+    <row r="629">
+      <c r="A629" t="inlineStr">
+        <is>
+          <t>PORSCHE</t>
+        </is>
+      </c>
+      <c r="B629" t="inlineStr">
+        <is>
+          <t>Panamera Sport Turismo</t>
+        </is>
+      </c>
+      <c r="C629" t="inlineStr">
+        <is>
+          <t>3.0 4 E-Hybrid</t>
+        </is>
+      </c>
+      <c r="D629" t="inlineStr">
+        <is>
+          <t>2017-01 ~ 2020-01</t>
+        </is>
+      </c>
+      <c r="E629" t="inlineStr">
+        <is>
+          <t>0583</t>
+        </is>
+      </c>
+      <c r="F629" t="inlineStr">
+        <is>
+          <t>AKG</t>
+        </is>
+      </c>
+      <c r="G629" t="inlineStr">
+        <is>
+          <t>04/2013 -</t>
+        </is>
+      </c>
+      <c r="H629" t="inlineStr">
+        <is>
+          <t>RDE047 + RDV021 | 45.142.000, RDE047 + RDV026 | 73.907.047</t>
+        </is>
+      </c>
+      <c r="I629" t="inlineStr">
+        <is>
+          <t>BH SENS</t>
+        </is>
+      </c>
+      <c r="J629" t="inlineStr">
+        <is>
+          <t>433</t>
+        </is>
+      </c>
+    </row>
+    <row r="630">
+      <c r="A630" t="inlineStr">
+        <is>
+          <t>PORSCHE</t>
+        </is>
+      </c>
+      <c r="B630" t="inlineStr">
+        <is>
+          <t>Panamera Sport Turismo</t>
+        </is>
+      </c>
+      <c r="C630" t="inlineStr">
+        <is>
+          <t>3.0 4 E-Hybrid</t>
+        </is>
+      </c>
+      <c r="D630" t="inlineStr">
+        <is>
+          <t>2020-01 ~ 2023-01</t>
+        </is>
+      </c>
+      <c r="E630" t="inlineStr">
+        <is>
+          <t>0583</t>
+        </is>
+      </c>
+      <c r="F630" t="inlineStr">
+        <is>
+          <t>AKG</t>
+        </is>
+      </c>
+      <c r="G630" t="inlineStr">
+        <is>
+          <t>04/2013 -</t>
+        </is>
+      </c>
+      <c r="H630" t="inlineStr">
+        <is>
+          <t>RDE047 + RDV021 | 45.142.000, RDE047 + RDV026 | 73.907.047</t>
+        </is>
+      </c>
+      <c r="I630" t="inlineStr">
+        <is>
+          <t>BH SENS</t>
+        </is>
+      </c>
+      <c r="J630" t="inlineStr">
+        <is>
+          <t>433</t>
+        </is>
+      </c>
+    </row>
+    <row r="631">
+      <c r="A631" t="inlineStr">
+        <is>
+          <t>PORSCHE</t>
+        </is>
+      </c>
+      <c r="B631" t="inlineStr">
+        <is>
+          <t>Panamera Sport Turismo</t>
+        </is>
+      </c>
+      <c r="C631" t="inlineStr">
+        <is>
+          <t>3.0 4S E-Hybrid</t>
+        </is>
+      </c>
+      <c r="D631" t="inlineStr">
+        <is>
+          <t>2020-01 ~ 2023-01</t>
+        </is>
+      </c>
+      <c r="E631" t="inlineStr">
+        <is>
+          <t>0583</t>
+        </is>
+      </c>
+      <c r="F631" t="inlineStr">
+        <is>
+          <t>AMQ</t>
+        </is>
+      </c>
+      <c r="G631" t="inlineStr">
+        <is>
+          <t>04/2013 -</t>
+        </is>
+      </c>
+      <c r="H631" t="inlineStr">
+        <is>
+          <t>RDE047 + RDV021 | 45.142.000, RDE047 + RDV026 | 73.907.047</t>
+        </is>
+      </c>
+      <c r="I631" t="inlineStr">
+        <is>
+          <t>BH SENS</t>
+        </is>
+      </c>
+      <c r="J631" t="inlineStr">
+        <is>
+          <t>433</t>
+        </is>
+      </c>
+    </row>
+    <row r="632">
+      <c r="A632" t="inlineStr">
+        <is>
+          <t>PORSCHE</t>
+        </is>
+      </c>
+      <c r="B632" t="inlineStr">
+        <is>
+          <t>Panamera Sport Turismo</t>
+        </is>
+      </c>
+      <c r="C632" t="inlineStr">
+        <is>
+          <t>4.0 GTS</t>
+        </is>
+      </c>
+      <c r="D632" t="inlineStr">
+        <is>
+          <t>2020-01 ~ 2023-01</t>
+        </is>
+      </c>
+      <c r="E632" t="inlineStr">
+        <is>
+          <t>0583</t>
+        </is>
+      </c>
+      <c r="F632" t="inlineStr">
+        <is>
+          <t>AMS</t>
+        </is>
+      </c>
+      <c r="G632" t="inlineStr">
+        <is>
+          <t>04/2013 -</t>
+        </is>
+      </c>
+      <c r="H632" t="inlineStr">
+        <is>
+          <t>RDE047 + RDV021 | 45.142.000, RDE047 + RDV026 | 73.907.047</t>
+        </is>
+      </c>
+      <c r="I632" t="inlineStr">
+        <is>
+          <t>BH SENS</t>
+        </is>
+      </c>
+      <c r="J632" t="inlineStr">
+        <is>
+          <t>433</t>
+        </is>
+      </c>
+    </row>
+    <row r="633">
+      <c r="A633" t="inlineStr">
+        <is>
+          <t>PORSCHE</t>
+        </is>
+      </c>
+      <c r="B633" t="inlineStr">
+        <is>
+          <t>Panamera Sport Turismo</t>
+        </is>
+      </c>
+      <c r="C633" t="inlineStr">
+        <is>
+          <t>4.0 Turbo S</t>
+        </is>
+      </c>
+      <c r="D633" t="inlineStr">
+        <is>
+          <t>2020-01 ~ 2023-01</t>
+        </is>
+      </c>
+      <c r="E633" t="inlineStr">
+        <is>
+          <t>0583</t>
+        </is>
+      </c>
+      <c r="F633" t="inlineStr">
+        <is>
+          <t>AMU</t>
+        </is>
+      </c>
+      <c r="G633" t="inlineStr">
+        <is>
+          <t>04/2013 -</t>
+        </is>
+      </c>
+      <c r="H633" t="inlineStr">
+        <is>
+          <t>RDE047 + RDV021 | 45.142.000, RDE047 + RDV026 | 73.907.047</t>
+        </is>
+      </c>
+      <c r="I633" t="inlineStr">
+        <is>
+          <t>BH SENS</t>
+        </is>
+      </c>
+      <c r="J633" t="inlineStr">
+        <is>
+          <t>433</t>
+        </is>
+      </c>
+    </row>
+    <row r="634">
+      <c r="A634" t="inlineStr">
+        <is>
+          <t>PORSCHE</t>
+        </is>
+      </c>
+      <c r="B634" t="inlineStr">
+        <is>
+          <t>Panamera Sport Turismo</t>
+        </is>
+      </c>
+      <c r="C634" t="inlineStr">
+        <is>
+          <t>4.0 Turbo S E-Hybrid</t>
+        </is>
+      </c>
+      <c r="D634" t="inlineStr">
+        <is>
+          <t>2017-01 ~ 2020-01</t>
+        </is>
+      </c>
+      <c r="E634" t="inlineStr">
+        <is>
+          <t>0583</t>
+        </is>
+      </c>
+      <c r="F634" t="inlineStr">
+        <is>
+          <t>AKD</t>
+        </is>
+      </c>
+      <c r="G634" t="inlineStr">
+        <is>
+          <t>04/2013 -</t>
+        </is>
+      </c>
+      <c r="H634" t="inlineStr">
+        <is>
+          <t>RDE047 + RDV021 | 45.142.000, RDE047 + RDV026 | 73.907.047</t>
+        </is>
+      </c>
+      <c r="I634" t="inlineStr">
+        <is>
+          <t>BH SENS</t>
+        </is>
+      </c>
+      <c r="J634" t="inlineStr">
+        <is>
+          <t>433</t>
+        </is>
+      </c>
+    </row>
+    <row r="635">
+      <c r="A635" t="inlineStr">
+        <is>
+          <t>PORSCHE</t>
+        </is>
+      </c>
+      <c r="B635" t="inlineStr">
+        <is>
+          <t>Panamera Sport Turismo</t>
+        </is>
+      </c>
+      <c r="C635" t="inlineStr">
+        <is>
+          <t>4.0 Turbo S E-Hybrid</t>
+        </is>
+      </c>
+      <c r="D635" t="inlineStr">
+        <is>
+          <t>2020-01 ~ 2023-01</t>
+        </is>
+      </c>
+      <c r="E635" t="inlineStr">
+        <is>
+          <t>0583</t>
+        </is>
+      </c>
+      <c r="F635" t="inlineStr">
+        <is>
+          <t>AMW</t>
+        </is>
+      </c>
+      <c r="G635" t="inlineStr">
+        <is>
+          <t>04/2013 -</t>
+        </is>
+      </c>
+      <c r="H635" t="inlineStr">
+        <is>
+          <t>RDE047 + RDV021 | 45.142.000, RDE047 + RDV026 | 73.907.047</t>
+        </is>
+      </c>
+      <c r="I635" t="inlineStr">
+        <is>
+          <t>BH SENS</t>
+        </is>
+      </c>
+      <c r="J635" t="inlineStr">
+        <is>
+          <t>433</t>
+        </is>
+      </c>
+    </row>
+    <row r="636">
+      <c r="A636" t="inlineStr">
+        <is>
+          <t>PORSCHE</t>
+        </is>
+      </c>
+      <c r="B636" t="inlineStr">
+        <is>
+          <t>Panamera Sport Turismo</t>
+        </is>
+      </c>
+      <c r="C636" t="inlineStr">
+        <is>
+          <t>4S</t>
+        </is>
+      </c>
+      <c r="D636" t="inlineStr">
+        <is>
+          <t>2017-01 ~ 2020-01</t>
+        </is>
+      </c>
+      <c r="E636" t="inlineStr">
+        <is>
+          <t>0583</t>
+        </is>
+      </c>
+      <c r="F636" t="inlineStr">
+        <is>
+          <t>AKF</t>
+        </is>
+      </c>
+      <c r="G636" t="inlineStr">
+        <is>
+          <t>04/2013 -</t>
+        </is>
+      </c>
+      <c r="H636" t="inlineStr">
+        <is>
+          <t>RDE047 + RDV021 | 45.142.000, RDE047 + RDV026 | 73.907.047</t>
+        </is>
+      </c>
+      <c r="I636" t="inlineStr">
+        <is>
+          <t>BH SENS</t>
+        </is>
+      </c>
+      <c r="J636" t="inlineStr">
+        <is>
+          <t>433</t>
+        </is>
+      </c>
+    </row>
+    <row r="637">
+      <c r="A637" t="inlineStr">
+        <is>
+          <t>PORSCHE</t>
+        </is>
+      </c>
+      <c r="B637" t="inlineStr">
+        <is>
+          <t>Panamera Sport Turismo</t>
+        </is>
+      </c>
+      <c r="C637" t="inlineStr">
+        <is>
+          <t>4S</t>
+        </is>
+      </c>
+      <c r="D637" t="inlineStr">
+        <is>
+          <t>2020-01 ~ 2023-01</t>
+        </is>
+      </c>
+      <c r="E637" t="inlineStr">
+        <is>
+          <t>0583</t>
+        </is>
+      </c>
+      <c r="F637" t="inlineStr">
+        <is>
+          <t>AKF</t>
+        </is>
+      </c>
+      <c r="G637" t="inlineStr">
+        <is>
+          <t>04/2013 -</t>
+        </is>
+      </c>
+      <c r="H637" t="inlineStr">
+        <is>
+          <t>RDE047 + RDV021 | 45.142.000, RDE047 + RDV026 | 73.907.047</t>
+        </is>
+      </c>
+      <c r="I637" t="inlineStr">
+        <is>
+          <t>BH SENS</t>
+        </is>
+      </c>
+      <c r="J637" t="inlineStr">
+        <is>
+          <t>433</t>
+        </is>
+      </c>
+    </row>
+    <row r="638">
+      <c r="A638" t="inlineStr">
+        <is>
+          <t>PORSCHE</t>
+        </is>
+      </c>
+      <c r="B638" t="inlineStr">
+        <is>
+          <t>Panamera Sport Turismo</t>
+        </is>
+      </c>
+      <c r="C638" t="inlineStr">
+        <is>
+          <t>4S Diesel</t>
+        </is>
+      </c>
+      <c r="D638" t="inlineStr">
+        <is>
+          <t>2017-01 ~ 2020-01</t>
+        </is>
+      </c>
+      <c r="E638" t="inlineStr">
+        <is>
+          <t>0583</t>
+        </is>
+      </c>
+      <c r="F638" t="inlineStr">
+        <is>
+          <t>AKI</t>
+        </is>
+      </c>
+      <c r="G638" t="inlineStr">
+        <is>
+          <t>04/2013 -</t>
+        </is>
+      </c>
+      <c r="H638" t="inlineStr">
+        <is>
+          <t>RDE047 + RDV021 | 45.142.000, RDE047 + RDV026 | 73.907.047</t>
+        </is>
+      </c>
+      <c r="I638" t="inlineStr">
+        <is>
+          <t>BH SENS</t>
+        </is>
+      </c>
+      <c r="J638" t="inlineStr">
+        <is>
+          <t>433</t>
+        </is>
+      </c>
+    </row>
+    <row r="639">
+      <c r="A639" t="inlineStr">
+        <is>
+          <t>PORSCHE</t>
+        </is>
+      </c>
+      <c r="B639" t="inlineStr">
+        <is>
+          <t>Panamera Sport Turismo</t>
+        </is>
+      </c>
+      <c r="C639" t="inlineStr">
+        <is>
+          <t>GTS</t>
+        </is>
+      </c>
+      <c r="D639" t="inlineStr">
+        <is>
+          <t>2019-01 ~ 2020-01</t>
+        </is>
+      </c>
+      <c r="E639" t="inlineStr">
+        <is>
+          <t>0583</t>
+        </is>
+      </c>
+      <c r="F639" t="inlineStr">
+        <is>
+          <t>ALB</t>
+        </is>
+      </c>
+      <c r="G639" t="inlineStr">
+        <is>
+          <t>04/2013 -</t>
+        </is>
+      </c>
+      <c r="H639" t="inlineStr">
+        <is>
+          <t>RDE047 + RDV021 | 45.142.000, RDE047 + RDV026 | 73.907.047</t>
+        </is>
+      </c>
+      <c r="I639" t="inlineStr">
+        <is>
+          <t>BH SENS</t>
+        </is>
+      </c>
+      <c r="J639" t="inlineStr">
+        <is>
+          <t>433</t>
+        </is>
+      </c>
+    </row>
+    <row r="640">
+      <c r="A640" t="inlineStr">
+        <is>
+          <t>PORSCHE</t>
+        </is>
+      </c>
+      <c r="B640" t="inlineStr">
+        <is>
+          <t>Panamera Sport Turismo</t>
+        </is>
+      </c>
+      <c r="C640" t="inlineStr">
+        <is>
+          <t>Turbo</t>
+        </is>
+      </c>
+      <c r="D640" t="inlineStr">
+        <is>
+          <t>2017-01 ~ 2020-01</t>
+        </is>
+      </c>
+      <c r="E640" t="inlineStr">
+        <is>
+          <t>0583</t>
+        </is>
+      </c>
+      <c r="F640" t="inlineStr">
+        <is>
+          <t>AKH</t>
+        </is>
+      </c>
+      <c r="G640" t="inlineStr">
+        <is>
+          <t>04/2013 -</t>
+        </is>
+      </c>
+      <c r="H640" t="inlineStr">
+        <is>
+          <t>RDE047 + RDV021 | 45.142.000, RDE047 + RDV026 | 73.907.047</t>
+        </is>
+      </c>
+      <c r="I640" t="inlineStr">
+        <is>
+          <t>BH SENS</t>
+        </is>
+      </c>
+      <c r="J640" t="inlineStr">
+        <is>
+          <t>433</t>
+        </is>
+      </c>
+    </row>
+    <row r="641">
+      <c r="A641" t="inlineStr">
+        <is>
+          <t>PORSCHE</t>
+        </is>
+      </c>
+      <c r="B641" t="inlineStr">
+        <is>
+          <t>Taycan</t>
+        </is>
+      </c>
+      <c r="C641" t="inlineStr">
+        <is>
+          <t>4 Performancebatterie</t>
+        </is>
+      </c>
+      <c r="D641" t="inlineStr">
+        <is>
+          <t>2024-01 ~ 至今</t>
+        </is>
+      </c>
+      <c r="E641" t="inlineStr">
+        <is>
+          <t>0583</t>
+        </is>
+      </c>
+      <c r="F641" t="inlineStr">
+        <is>
+          <t>AOQ</t>
+        </is>
+      </c>
+      <c r="G641" t="inlineStr">
+        <is>
+          <t>03/2024 -, 06/2019 - 02/2024</t>
+        </is>
+      </c>
+      <c r="H641" t="inlineStr">
+        <is>
+          <t>RDE047 + RDV021 | 45.142.000, RDE047 + RDV026 | 73.907.047, RDE254+RDV021, RDE254+RDV026</t>
+        </is>
+      </c>
+      <c r="I641" t="inlineStr">
+        <is>
+          <t>BH SENS</t>
+        </is>
+      </c>
+      <c r="J641" t="inlineStr">
+        <is>
+          <t>433</t>
+        </is>
+      </c>
+    </row>
+    <row r="642">
+      <c r="A642" t="inlineStr">
+        <is>
+          <t>PORSCHE</t>
+        </is>
+      </c>
+      <c r="B642" t="inlineStr">
+        <is>
+          <t>Taycan</t>
+        </is>
+      </c>
+      <c r="C642" t="inlineStr">
+        <is>
+          <t>4 Performancebatterie Plus</t>
+        </is>
+      </c>
+      <c r="D642" t="inlineStr">
+        <is>
+          <t>2024-01 ~ 至今</t>
+        </is>
+      </c>
+      <c r="E642" t="inlineStr">
+        <is>
+          <t>0583</t>
+        </is>
+      </c>
+      <c r="F642" t="inlineStr">
+        <is>
+          <t>AOP</t>
+        </is>
+      </c>
+      <c r="G642" t="inlineStr">
+        <is>
+          <t>03/2024 -, 06/2019 - 02/2024</t>
+        </is>
+      </c>
+      <c r="H642" t="inlineStr">
+        <is>
+          <t>RDE047 + RDV021 | 45.142.000, RDE047 + RDV026 | 73.907.047, RDE254+RDV021, RDE254+RDV026</t>
+        </is>
+      </c>
+      <c r="I642" t="inlineStr">
+        <is>
+          <t>BH SENS</t>
+        </is>
+      </c>
+      <c r="J642" t="inlineStr">
+        <is>
+          <t>433</t>
+        </is>
+      </c>
+    </row>
+    <row r="643">
+      <c r="A643" t="inlineStr">
+        <is>
+          <t>PORSCHE</t>
+        </is>
+      </c>
+      <c r="B643" t="inlineStr">
+        <is>
+          <t>Taycan</t>
+        </is>
+      </c>
+      <c r="C643" t="inlineStr">
+        <is>
+          <t>4S</t>
+        </is>
+      </c>
+      <c r="D643" t="inlineStr">
+        <is>
+          <t>2020-01 ~ 2024-01</t>
+        </is>
+      </c>
+      <c r="E643" t="inlineStr">
+        <is>
+          <t>0583</t>
+        </is>
+      </c>
+      <c r="F643" t="inlineStr">
+        <is>
+          <t>ALZ</t>
+        </is>
+      </c>
+      <c r="G643" t="inlineStr">
+        <is>
+          <t>06/2019 - 02/2024</t>
+        </is>
+      </c>
+      <c r="H643" t="inlineStr">
+        <is>
+          <t>RDE047 + RDV021 | 45.142.000, RDE047 + RDV026 | 73.907.047</t>
+        </is>
+      </c>
+      <c r="I643" t="inlineStr">
+        <is>
+          <t>BH SENS</t>
+        </is>
+      </c>
+      <c r="J643" t="inlineStr">
+        <is>
+          <t>433</t>
+        </is>
+      </c>
+    </row>
+    <row r="644">
+      <c r="A644" t="inlineStr">
+        <is>
+          <t>PORSCHE</t>
+        </is>
+      </c>
+      <c r="B644" t="inlineStr">
+        <is>
+          <t>Taycan</t>
+        </is>
+      </c>
+      <c r="C644" t="inlineStr">
+        <is>
+          <t>4S</t>
+        </is>
+      </c>
+      <c r="D644" t="inlineStr">
+        <is>
+          <t>2020-01 ~ 2024-01</t>
+        </is>
+      </c>
+      <c r="E644" t="inlineStr">
+        <is>
+          <t>0583</t>
+        </is>
+      </c>
+      <c r="F644" t="inlineStr">
+        <is>
+          <t>AMA</t>
+        </is>
+      </c>
+      <c r="G644" t="inlineStr">
+        <is>
+          <t>06/2019 - 02/2024</t>
+        </is>
+      </c>
+      <c r="H644" t="inlineStr">
+        <is>
+          <t>RDE047 + RDV021 | 45.142.000, RDE047 + RDV026 | 73.907.047</t>
+        </is>
+      </c>
+      <c r="I644" t="inlineStr">
+        <is>
+          <t>BH SENS</t>
+        </is>
+      </c>
+      <c r="J644" t="inlineStr">
+        <is>
+          <t>433</t>
+        </is>
+      </c>
+    </row>
+    <row r="645">
+      <c r="A645" t="inlineStr">
+        <is>
+          <t>PORSCHE</t>
+        </is>
+      </c>
+      <c r="B645" t="inlineStr">
+        <is>
+          <t>Taycan</t>
+        </is>
+      </c>
+      <c r="C645" t="inlineStr">
+        <is>
+          <t>4S Performancebatterie</t>
+        </is>
+      </c>
+      <c r="D645" t="inlineStr">
+        <is>
+          <t>2024-01 ~ 至今</t>
+        </is>
+      </c>
+      <c r="E645" t="inlineStr">
+        <is>
+          <t>0583</t>
+        </is>
+      </c>
+      <c r="F645" t="inlineStr">
+        <is>
+          <t>AOO</t>
+        </is>
+      </c>
+      <c r="G645" t="inlineStr">
+        <is>
+          <t>03/2024 -, 06/2019 - 02/2024</t>
+        </is>
+      </c>
+      <c r="H645" t="inlineStr">
+        <is>
+          <t>RDE047 + RDV021 | 45.142.000, RDE047 + RDV026 | 73.907.047, RDE254+RDV021, RDE254+RDV026</t>
+        </is>
+      </c>
+      <c r="I645" t="inlineStr">
+        <is>
+          <t>BH SENS</t>
+        </is>
+      </c>
+      <c r="J645" t="inlineStr">
+        <is>
+          <t>433</t>
+        </is>
+      </c>
+    </row>
+    <row r="646">
+      <c r="A646" t="inlineStr">
+        <is>
+          <t>PORSCHE</t>
+        </is>
+      </c>
+      <c r="B646" t="inlineStr">
+        <is>
+          <t>Taycan</t>
+        </is>
+      </c>
+      <c r="C646" t="inlineStr">
+        <is>
+          <t>4S Performancebatterie Plus</t>
+        </is>
+      </c>
+      <c r="D646" t="inlineStr">
+        <is>
+          <t>2024-01 ~ 至今</t>
+        </is>
+      </c>
+      <c r="E646" t="inlineStr">
+        <is>
+          <t>0583</t>
+        </is>
+      </c>
+      <c r="F646" t="inlineStr">
+        <is>
+          <t>AON</t>
+        </is>
+      </c>
+      <c r="G646" t="inlineStr">
+        <is>
+          <t>03/2024 -, 06/2019 - 02/2024</t>
+        </is>
+      </c>
+      <c r="H646" t="inlineStr">
+        <is>
+          <t>RDE047 + RDV021 | 45.142.000, RDE047 + RDV026 | 73.907.047, RDE254+RDV021, RDE254+RDV026</t>
+        </is>
+      </c>
+      <c r="I646" t="inlineStr">
+        <is>
+          <t>BH SENS</t>
+        </is>
+      </c>
+      <c r="J646" t="inlineStr">
+        <is>
+          <t>433</t>
+        </is>
+      </c>
+    </row>
+    <row r="647">
+      <c r="A647" t="inlineStr">
+        <is>
+          <t>PORSCHE</t>
+        </is>
+      </c>
+      <c r="B647" t="inlineStr">
+        <is>
+          <t>Taycan</t>
+        </is>
+      </c>
+      <c r="C647" t="inlineStr">
+        <is>
+          <t>GTS</t>
+        </is>
+      </c>
+      <c r="D647" t="inlineStr">
+        <is>
+          <t>2020-01 ~ 2024-01</t>
+        </is>
+      </c>
+      <c r="E647" t="inlineStr">
+        <is>
+          <t>0583</t>
+        </is>
+      </c>
+      <c r="F647" t="inlineStr">
+        <is>
+          <t>ALY</t>
+        </is>
+      </c>
+      <c r="G647" t="inlineStr">
+        <is>
+          <t>06/2019 - 02/2024</t>
+        </is>
+      </c>
+      <c r="H647" t="inlineStr">
+        <is>
+          <t>RDE047 + RDV021 | 45.142.000, RDE047 + RDV026 | 73.907.047</t>
+        </is>
+      </c>
+      <c r="I647" t="inlineStr">
+        <is>
+          <t>BH SENS</t>
+        </is>
+      </c>
+      <c r="J647" t="inlineStr">
+        <is>
+          <t>433</t>
+        </is>
+      </c>
+    </row>
+    <row r="648">
+      <c r="A648" t="inlineStr">
+        <is>
+          <t>PORSCHE</t>
+        </is>
+      </c>
+      <c r="B648" t="inlineStr">
+        <is>
+          <t>Taycan</t>
+        </is>
+      </c>
+      <c r="C648" t="inlineStr">
+        <is>
+          <t>GTS Performancebatterie Plus</t>
+        </is>
+      </c>
+      <c r="D648" t="inlineStr">
+        <is>
+          <t>2024-01 ~ 至今</t>
+        </is>
+      </c>
+      <c r="E648" t="inlineStr">
+        <is>
+          <t>0583</t>
+        </is>
+      </c>
+      <c r="F648" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="G648" t="inlineStr">
+        <is>
+          <t>03/2024 -, 06/2019 - 02/2024</t>
+        </is>
+      </c>
+      <c r="H648" t="inlineStr">
+        <is>
+          <t>RDE047 + RDV021 | 45.142.000, RDE047 + RDV026 | 73.907.047, RDE254+RDV021, RDE254+RDV026</t>
+        </is>
+      </c>
+      <c r="I648" t="inlineStr">
+        <is>
+          <t>BH SENS</t>
+        </is>
+      </c>
+      <c r="J648" t="inlineStr">
+        <is>
+          <t>433</t>
+        </is>
+      </c>
+    </row>
+    <row r="649">
+      <c r="A649" t="inlineStr">
+        <is>
+          <t>PORSCHE</t>
+        </is>
+      </c>
+      <c r="B649" t="inlineStr">
+        <is>
+          <t>Taycan</t>
+        </is>
+      </c>
+      <c r="C649" t="inlineStr">
+        <is>
+          <t>Performancebatterie</t>
+        </is>
+      </c>
+      <c r="D649" t="inlineStr">
+        <is>
+          <t>2024-01 ~ 至今</t>
+        </is>
+      </c>
+      <c r="E649" t="inlineStr">
+        <is>
+          <t>0583</t>
+        </is>
+      </c>
+      <c r="F649" t="inlineStr">
+        <is>
+          <t>AOS</t>
+        </is>
+      </c>
+      <c r="G649" t="inlineStr">
+        <is>
+          <t>03/2024 -, 06/2019 - 02/2024</t>
+        </is>
+      </c>
+      <c r="H649" t="inlineStr">
+        <is>
+          <t>RDE047 + RDV021 | 45.142.000, RDE047 + RDV026 | 73.907.047, RDE254+RDV021, RDE254+RDV026</t>
+        </is>
+      </c>
+      <c r="I649" t="inlineStr">
+        <is>
+          <t>BH SENS</t>
+        </is>
+      </c>
+      <c r="J649" t="inlineStr">
+        <is>
+          <t>433</t>
+        </is>
+      </c>
+    </row>
+    <row r="650">
+      <c r="A650" t="inlineStr">
+        <is>
+          <t>PORSCHE</t>
+        </is>
+      </c>
+      <c r="B650" t="inlineStr">
+        <is>
+          <t>Taycan</t>
+        </is>
+      </c>
+      <c r="C650" t="inlineStr">
+        <is>
+          <t>Performancebatterie Plus</t>
+        </is>
+      </c>
+      <c r="D650" t="inlineStr">
+        <is>
+          <t>2024-01 ~ 至今</t>
+        </is>
+      </c>
+      <c r="E650" t="inlineStr">
+        <is>
+          <t>0583</t>
+        </is>
+      </c>
+      <c r="F650" t="inlineStr">
+        <is>
+          <t>AOR</t>
+        </is>
+      </c>
+      <c r="G650" t="inlineStr">
+        <is>
+          <t>03/2024 -, 06/2019 - 02/2024</t>
+        </is>
+      </c>
+      <c r="H650" t="inlineStr">
+        <is>
+          <t>RDE047 + RDV021 | 45.142.000, RDE047 + RDV026 | 73.907.047, RDE254+RDV021, RDE254+RDV026</t>
+        </is>
+      </c>
+      <c r="I650" t="inlineStr">
+        <is>
+          <t>BH SENS</t>
+        </is>
+      </c>
+      <c r="J650" t="inlineStr">
+        <is>
+          <t>433</t>
+        </is>
+      </c>
+    </row>
+    <row r="651">
+      <c r="A651" t="inlineStr">
+        <is>
+          <t>PORSCHE</t>
+        </is>
+      </c>
+      <c r="B651" t="inlineStr">
+        <is>
+          <t>Taycan</t>
+        </is>
+      </c>
+      <c r="C651" t="inlineStr">
+        <is>
+          <t>Turbo</t>
+        </is>
+      </c>
+      <c r="D651" t="inlineStr">
+        <is>
+          <t>2020-01 ~ 2024-01</t>
+        </is>
+      </c>
+      <c r="E651" t="inlineStr">
+        <is>
+          <t>0583</t>
+        </is>
+      </c>
+      <c r="F651" t="inlineStr">
+        <is>
+          <t>ALY</t>
+        </is>
+      </c>
+      <c r="G651" t="inlineStr">
+        <is>
+          <t>06/2019 - 02/2024</t>
+        </is>
+      </c>
+      <c r="H651" t="inlineStr">
+        <is>
+          <t>RDE047 + RDV021 | 45.142.000, RDE047 + RDV026 | 73.907.047</t>
+        </is>
+      </c>
+      <c r="I651" t="inlineStr">
+        <is>
+          <t>BH SENS</t>
+        </is>
+      </c>
+      <c r="J651" t="inlineStr">
+        <is>
+          <t>433</t>
+        </is>
+      </c>
+    </row>
+    <row r="652">
+      <c r="A652" t="inlineStr">
+        <is>
+          <t>PORSCHE</t>
+        </is>
+      </c>
+      <c r="B652" t="inlineStr">
+        <is>
+          <t>Taycan</t>
+        </is>
+      </c>
+      <c r="C652" t="inlineStr">
+        <is>
+          <t>Turbo GT Manthey</t>
+        </is>
+      </c>
+      <c r="D652" t="inlineStr">
+        <is>
+          <t>2026-01 ~ 至今</t>
+        </is>
+      </c>
+      <c r="E652" t="inlineStr">
+        <is>
+          <t>0583</t>
+        </is>
+      </c>
+      <c r="F652" t="inlineStr">
+        <is>
+          <t>APR</t>
+        </is>
+      </c>
+      <c r="G652" t="inlineStr">
+        <is>
+          <t>03/2024 -</t>
+        </is>
+      </c>
+      <c r="H652" t="inlineStr">
+        <is>
+          <t>RDE254+RDV021, RDE254+RDV026</t>
+        </is>
+      </c>
+      <c r="I652" t="inlineStr">
+        <is>
+          <t>BH SENS</t>
+        </is>
+      </c>
+      <c r="J652" t="inlineStr">
+        <is>
+          <t>433</t>
+        </is>
+      </c>
+    </row>
+    <row r="653">
+      <c r="A653" t="inlineStr">
+        <is>
+          <t>PORSCHE</t>
+        </is>
+      </c>
+      <c r="B653" t="inlineStr">
+        <is>
+          <t>Taycan</t>
+        </is>
+      </c>
+      <c r="C653" t="inlineStr">
+        <is>
+          <t>Turbo GT Performancebatterie Plus</t>
+        </is>
+      </c>
+      <c r="D653" t="inlineStr">
+        <is>
+          <t>2024-01 ~ 至今</t>
+        </is>
+      </c>
+      <c r="E653" t="inlineStr">
+        <is>
+          <t>0583</t>
+        </is>
+      </c>
+      <c r="F653" t="inlineStr">
+        <is>
+          <t>AOL</t>
+        </is>
+      </c>
+      <c r="G653" t="inlineStr">
+        <is>
+          <t>03/2024 -, 06/2019 - 02/2024</t>
+        </is>
+      </c>
+      <c r="H653" t="inlineStr">
+        <is>
+          <t>RDE047 + RDV021 | 45.142.000, RDE047 + RDV026 | 73.907.047, RDE254+RDV021, RDE254+RDV026</t>
+        </is>
+      </c>
+      <c r="I653" t="inlineStr">
+        <is>
+          <t>BH SENS</t>
+        </is>
+      </c>
+      <c r="J653" t="inlineStr">
+        <is>
+          <t>433</t>
+        </is>
+      </c>
+    </row>
+    <row r="654">
+      <c r="A654" t="inlineStr">
+        <is>
+          <t>PORSCHE</t>
+        </is>
+      </c>
+      <c r="B654" t="inlineStr">
+        <is>
+          <t>Taycan</t>
+        </is>
+      </c>
+      <c r="C654" t="inlineStr">
+        <is>
+          <t>Turbo Performancebatterie Plus</t>
+        </is>
+      </c>
+      <c r="D654" t="inlineStr">
+        <is>
+          <t>2024-01 ~ 至今</t>
+        </is>
+      </c>
+      <c r="E654" t="inlineStr">
+        <is>
+          <t>0583</t>
+        </is>
+      </c>
+      <c r="F654" t="inlineStr">
+        <is>
+          <t>AOM</t>
+        </is>
+      </c>
+      <c r="G654" t="inlineStr">
+        <is>
+          <t>03/2024 -, 06/2019 - 02/2024</t>
+        </is>
+      </c>
+      <c r="H654" t="inlineStr">
+        <is>
+          <t>RDE047 + RDV021 | 45.142.000, RDE047 + RDV026 | 73.907.047, RDE254+RDV021, RDE254+RDV026</t>
+        </is>
+      </c>
+      <c r="I654" t="inlineStr">
+        <is>
+          <t>BH SENS</t>
+        </is>
+      </c>
+      <c r="J654" t="inlineStr">
+        <is>
+          <t>433</t>
+        </is>
+      </c>
+    </row>
+    <row r="655">
+      <c r="A655" t="inlineStr">
+        <is>
+          <t>PORSCHE</t>
+        </is>
+      </c>
+      <c r="B655" t="inlineStr">
+        <is>
+          <t>Taycan</t>
+        </is>
+      </c>
+      <c r="C655" t="inlineStr">
+        <is>
+          <t>Turbo S</t>
+        </is>
+      </c>
+      <c r="D655" t="inlineStr">
+        <is>
+          <t>2020-01 ~ 2024-01</t>
+        </is>
+      </c>
+      <c r="E655" t="inlineStr">
+        <is>
+          <t>0583</t>
+        </is>
+      </c>
+      <c r="F655" t="inlineStr">
+        <is>
+          <t>ALY</t>
+        </is>
+      </c>
+      <c r="G655" t="inlineStr">
+        <is>
+          <t>06/2019 - 02/2024</t>
+        </is>
+      </c>
+      <c r="H655" t="inlineStr">
+        <is>
+          <t>RDE047 + RDV021 | 45.142.000, RDE047 + RDV026 | 73.907.047</t>
+        </is>
+      </c>
+      <c r="I655" t="inlineStr">
+        <is>
+          <t>BH SENS</t>
+        </is>
+      </c>
+      <c r="J655" t="inlineStr">
+        <is>
+          <t>433</t>
+        </is>
+      </c>
+    </row>
+    <row r="656">
+      <c r="A656" t="inlineStr">
+        <is>
+          <t>PORSCHE</t>
+        </is>
+      </c>
+      <c r="B656" t="inlineStr">
+        <is>
+          <t>Taycan</t>
+        </is>
+      </c>
+      <c r="C656" t="inlineStr">
+        <is>
+          <t>Turbo S Performancebatterie Plus</t>
+        </is>
+      </c>
+      <c r="D656" t="inlineStr">
+        <is>
+          <t>2024-01 ~ 至今</t>
+        </is>
+      </c>
+      <c r="E656" t="inlineStr">
+        <is>
+          <t>0583</t>
+        </is>
+      </c>
+      <c r="F656" t="inlineStr">
+        <is>
+          <t>AOK</t>
+        </is>
+      </c>
+      <c r="G656" t="inlineStr">
+        <is>
+          <t>03/2024 -, 06/2019 - 02/2024</t>
+        </is>
+      </c>
+      <c r="H656" t="inlineStr">
+        <is>
+          <t>RDE047 + RDV021 | 45.142.000, RDE047 + RDV026 | 73.907.047, RDE254+RDV021, RDE254+RDV026</t>
+        </is>
+      </c>
+      <c r="I656" t="inlineStr">
+        <is>
+          <t>BH SENS</t>
+        </is>
+      </c>
+      <c r="J656" t="inlineStr">
+        <is>
+          <t>433</t>
+        </is>
+      </c>
+    </row>
+    <row r="657">
+      <c r="A657" t="inlineStr">
+        <is>
+          <t>PORSCHE</t>
+        </is>
+      </c>
+      <c r="B657" t="inlineStr">
+        <is>
+          <t>Taycan</t>
+        </is>
+      </c>
+      <c r="C657" t="inlineStr">
+        <is>
+          <t>electric</t>
+        </is>
+      </c>
+      <c r="D657" t="inlineStr">
+        <is>
+          <t>2021-01 ~ 2024-01</t>
+        </is>
+      </c>
+      <c r="E657" t="inlineStr">
+        <is>
+          <t>0583</t>
+        </is>
+      </c>
+      <c r="F657" t="inlineStr">
+        <is>
+          <t>ANJ</t>
+        </is>
+      </c>
+      <c r="G657" t="inlineStr">
+        <is>
+          <t>06/2019 - 02/2024</t>
+        </is>
+      </c>
+      <c r="H657" t="inlineStr">
+        <is>
+          <t>RDE047 + RDV021 | 45.142.000, RDE047 + RDV026 | 73.907.047</t>
+        </is>
+      </c>
+      <c r="I657" t="inlineStr">
+        <is>
+          <t>BH SENS</t>
+        </is>
+      </c>
+      <c r="J657" t="inlineStr">
+        <is>
+          <t>433</t>
+        </is>
+      </c>
+    </row>
+    <row r="658">
+      <c r="A658" t="inlineStr">
+        <is>
+          <t>PORSCHE</t>
+        </is>
+      </c>
+      <c r="B658" t="inlineStr">
+        <is>
+          <t>Taycan Cross Turismo</t>
+        </is>
+      </c>
+      <c r="C658" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D658" t="inlineStr">
+        <is>
+          <t>2021-01 ~ 2024-01</t>
+        </is>
+      </c>
+      <c r="E658" t="inlineStr">
+        <is>
+          <t>0583</t>
+        </is>
+      </c>
+      <c r="F658" t="inlineStr">
+        <is>
+          <t>ANI</t>
+        </is>
+      </c>
+      <c r="G658" t="inlineStr">
+        <is>
+          <t>06/2019 - 02/2024</t>
+        </is>
+      </c>
+      <c r="H658" t="inlineStr">
+        <is>
+          <t>RDE047 + RDV021 | 45.142.000, RDE047 + RDV026 | 73.907.047</t>
+        </is>
+      </c>
+      <c r="I658" t="inlineStr">
+        <is>
+          <t>BH SENS</t>
+        </is>
+      </c>
+      <c r="J658" t="inlineStr">
+        <is>
+          <t>433</t>
+        </is>
+      </c>
+    </row>
+    <row r="659">
+      <c r="A659" t="inlineStr">
+        <is>
+          <t>PORSCHE</t>
+        </is>
+      </c>
+      <c r="B659" t="inlineStr">
+        <is>
+          <t>Taycan Cross Turismo</t>
+        </is>
+      </c>
+      <c r="C659" t="inlineStr">
+        <is>
+          <t>4 Performancebatterie Plus</t>
+        </is>
+      </c>
+      <c r="D659" t="inlineStr">
+        <is>
+          <t>2024-01 ~ 至今</t>
+        </is>
+      </c>
+      <c r="E659" t="inlineStr">
+        <is>
+          <t>0583</t>
+        </is>
+      </c>
+      <c r="F659" t="inlineStr">
+        <is>
+          <t>AOX</t>
+        </is>
+      </c>
+      <c r="G659" t="inlineStr">
+        <is>
+          <t>03/2024 -, 06/2019 - 02/2024</t>
+        </is>
+      </c>
+      <c r="H659" t="inlineStr">
+        <is>
+          <t>RDE047 + RDV021 | 45.142.000, RDE047 + RDV026 | 73.907.047, RDE254+RDV021, RDE254+RDV026</t>
+        </is>
+      </c>
+      <c r="I659" t="inlineStr">
+        <is>
+          <t>BH SENS</t>
+        </is>
+      </c>
+      <c r="J659" t="inlineStr">
+        <is>
+          <t>433</t>
+        </is>
+      </c>
+    </row>
+    <row r="660">
+      <c r="A660" t="inlineStr">
+        <is>
+          <t>PORSCHE</t>
+        </is>
+      </c>
+      <c r="B660" t="inlineStr">
+        <is>
+          <t>Taycan Cross Turismo</t>
+        </is>
+      </c>
+      <c r="C660" t="inlineStr">
+        <is>
+          <t>4S</t>
+        </is>
+      </c>
+      <c r="D660" t="inlineStr">
+        <is>
+          <t>2021-01 ~ 2024-01</t>
+        </is>
+      </c>
+      <c r="E660" t="inlineStr">
+        <is>
+          <t>0583</t>
+        </is>
+      </c>
+      <c r="F660" t="inlineStr">
+        <is>
+          <t>ANI</t>
+        </is>
+      </c>
+      <c r="G660" t="inlineStr">
+        <is>
+          <t>06/2019 - 02/2024</t>
+        </is>
+      </c>
+      <c r="H660" t="inlineStr">
+        <is>
+          <t>RDE047 + RDV021 | 45.142.000, RDE047 + RDV026 | 73.907.047</t>
+        </is>
+      </c>
+      <c r="I660" t="inlineStr">
+        <is>
+          <t>BH SENS</t>
+        </is>
+      </c>
+      <c r="J660" t="inlineStr">
+        <is>
+          <t>433</t>
+        </is>
+      </c>
+    </row>
+    <row r="661">
+      <c r="A661" t="inlineStr">
+        <is>
+          <t>PORSCHE</t>
+        </is>
+      </c>
+      <c r="B661" t="inlineStr">
+        <is>
+          <t>Taycan Cross Turismo</t>
+        </is>
+      </c>
+      <c r="C661" t="inlineStr">
+        <is>
+          <t>4S Performancebatterie Plus</t>
+        </is>
+      </c>
+      <c r="D661" t="inlineStr">
+        <is>
+          <t>2024-01 ~ 至今</t>
+        </is>
+      </c>
+      <c r="E661" t="inlineStr">
+        <is>
+          <t>0583</t>
+        </is>
+      </c>
+      <c r="F661" t="inlineStr">
+        <is>
+          <t>AOV</t>
+        </is>
+      </c>
+      <c r="G661" t="inlineStr">
+        <is>
+          <t>03/2024 -, 06/2019 - 02/2024</t>
+        </is>
+      </c>
+      <c r="H661" t="inlineStr">
+        <is>
+          <t>RDE047 + RDV021 | 45.142.000, RDE047 + RDV026 | 73.907.047, RDE254+RDV021, RDE254+RDV026</t>
+        </is>
+      </c>
+      <c r="I661" t="inlineStr">
+        <is>
+          <t>BH SENS</t>
+        </is>
+      </c>
+      <c r="J661" t="inlineStr">
+        <is>
+          <t>433</t>
+        </is>
+      </c>
+    </row>
+    <row r="662">
+      <c r="A662" t="inlineStr">
+        <is>
+          <t>PORSCHE</t>
+        </is>
+      </c>
+      <c r="B662" t="inlineStr">
+        <is>
+          <t>Taycan Cross Turismo</t>
+        </is>
+      </c>
+      <c r="C662" t="inlineStr">
+        <is>
+          <t>Turbo</t>
+        </is>
+      </c>
+      <c r="D662" t="inlineStr">
+        <is>
+          <t>2021-01 ~ 2024-01</t>
+        </is>
+      </c>
+      <c r="E662" t="inlineStr">
+        <is>
+          <t>0583</t>
+        </is>
+      </c>
+      <c r="F662" t="inlineStr">
+        <is>
+          <t>ANH</t>
+        </is>
+      </c>
+      <c r="G662" t="inlineStr">
+        <is>
+          <t>06/2019 - 02/2024</t>
+        </is>
+      </c>
+      <c r="H662" t="inlineStr">
+        <is>
+          <t>RDE047 + RDV021 | 45.142.000, RDE047 + RDV026 | 73.907.047</t>
+        </is>
+      </c>
+      <c r="I662" t="inlineStr">
+        <is>
+          <t>BH SENS</t>
+        </is>
+      </c>
+      <c r="J662" t="inlineStr">
+        <is>
+          <t>433</t>
+        </is>
+      </c>
+    </row>
+    <row r="663">
+      <c r="A663" t="inlineStr">
+        <is>
+          <t>PORSCHE</t>
+        </is>
+      </c>
+      <c r="B663" t="inlineStr">
+        <is>
+          <t>Taycan Cross Turismo</t>
+        </is>
+      </c>
+      <c r="C663" t="inlineStr">
+        <is>
+          <t>Turbo Performancebatterie Plus</t>
+        </is>
+      </c>
+      <c r="D663" t="inlineStr">
+        <is>
+          <t>2024-01 ~ 至今</t>
+        </is>
+      </c>
+      <c r="E663" t="inlineStr">
+        <is>
+          <t>0583</t>
+        </is>
+      </c>
+      <c r="F663" t="inlineStr">
+        <is>
+          <t>AOU</t>
+        </is>
+      </c>
+      <c r="G663" t="inlineStr">
+        <is>
+          <t>03/2024 -, 06/2019 - 02/2024</t>
+        </is>
+      </c>
+      <c r="H663" t="inlineStr">
+        <is>
+          <t>RDE047 + RDV021 | 45.142.000, RDE047 + RDV026 | 73.907.047, RDE254+RDV021, RDE254+RDV026</t>
+        </is>
+      </c>
+      <c r="I663" t="inlineStr">
+        <is>
+          <t>BH SENS</t>
+        </is>
+      </c>
+      <c r="J663" t="inlineStr">
+        <is>
+          <t>433</t>
+        </is>
+      </c>
+    </row>
+    <row r="664">
+      <c r="A664" t="inlineStr">
+        <is>
+          <t>PORSCHE</t>
+        </is>
+      </c>
+      <c r="B664" t="inlineStr">
+        <is>
+          <t>Taycan Cross Turismo</t>
+        </is>
+      </c>
+      <c r="C664" t="inlineStr">
+        <is>
+          <t>Turbo S</t>
+        </is>
+      </c>
+      <c r="D664" t="inlineStr">
+        <is>
+          <t>2021-01 ~ 2024-01</t>
+        </is>
+      </c>
+      <c r="E664" t="inlineStr">
+        <is>
+          <t>0583</t>
+        </is>
+      </c>
+      <c r="F664" t="inlineStr">
+        <is>
+          <t>ANH</t>
+        </is>
+      </c>
+      <c r="G664" t="inlineStr">
+        <is>
+          <t>06/2019 - 02/2024</t>
+        </is>
+      </c>
+      <c r="H664" t="inlineStr">
+        <is>
+          <t>RDE047 + RDV021 | 45.142.000, RDE047 + RDV026 | 73.907.047</t>
+        </is>
+      </c>
+      <c r="I664" t="inlineStr">
+        <is>
+          <t>BH SENS</t>
+        </is>
+      </c>
+      <c r="J664" t="inlineStr">
+        <is>
+          <t>433</t>
+        </is>
+      </c>
+    </row>
+    <row r="665">
+      <c r="A665" t="inlineStr">
+        <is>
+          <t>PORSCHE</t>
+        </is>
+      </c>
+      <c r="B665" t="inlineStr">
+        <is>
+          <t>Taycan Cross Turismo</t>
+        </is>
+      </c>
+      <c r="C665" t="inlineStr">
+        <is>
+          <t>Turbo S Performancebatterie Plus</t>
+        </is>
+      </c>
+      <c r="D665" t="inlineStr">
+        <is>
+          <t>2024-01 ~ 至今</t>
+        </is>
+      </c>
+      <c r="E665" t="inlineStr">
+        <is>
+          <t>0583</t>
+        </is>
+      </c>
+      <c r="F665" t="inlineStr">
+        <is>
+          <t>AOT</t>
+        </is>
+      </c>
+      <c r="G665" t="inlineStr">
+        <is>
+          <t>03/2024 -, 06/2019 - 02/2024</t>
+        </is>
+      </c>
+      <c r="H665" t="inlineStr">
+        <is>
+          <t>RDE047 + RDV021 | 45.142.000, RDE047 + RDV026 | 73.907.047, RDE254+RDV021, RDE254+RDV026</t>
+        </is>
+      </c>
+      <c r="I665" t="inlineStr">
+        <is>
+          <t>BH SENS</t>
+        </is>
+      </c>
+      <c r="J665" t="inlineStr">
+        <is>
+          <t>433</t>
+        </is>
+      </c>
+    </row>
+    <row r="666">
+      <c r="A666" t="inlineStr">
+        <is>
+          <t>PORSCHE</t>
+        </is>
+      </c>
+      <c r="B666" t="inlineStr">
+        <is>
+          <t>Taycan Sport Turismo</t>
+        </is>
+      </c>
+      <c r="C666" t="inlineStr">
+        <is>
+          <t>4S</t>
+        </is>
+      </c>
+      <c r="D666" t="inlineStr">
+        <is>
+          <t>2021-01 ~ 2024-01</t>
+        </is>
+      </c>
+      <c r="E666" t="inlineStr">
+        <is>
+          <t>0583</t>
+        </is>
+      </c>
+      <c r="F666" t="inlineStr">
+        <is>
+          <t>ANI</t>
+        </is>
+      </c>
+      <c r="G666" t="inlineStr">
+        <is>
+          <t>06/2019 - 02/2024</t>
+        </is>
+      </c>
+      <c r="H666" t="inlineStr">
+        <is>
+          <t>RDE047 + RDV021 | 45.142.000, RDE047 + RDV026 | 73.907.047</t>
+        </is>
+      </c>
+      <c r="I666" t="inlineStr">
+        <is>
+          <t>BH SENS</t>
+        </is>
+      </c>
+      <c r="J666" t="inlineStr">
+        <is>
+          <t>433</t>
+        </is>
+      </c>
+    </row>
+    <row r="667">
+      <c r="A667" t="inlineStr">
+        <is>
+          <t>PORSCHE</t>
+        </is>
+      </c>
+      <c r="B667" t="inlineStr">
+        <is>
+          <t>Taycan Sport Turismo</t>
+        </is>
+      </c>
+      <c r="C667" t="inlineStr">
+        <is>
+          <t>4S</t>
+        </is>
+      </c>
+      <c r="D667" t="inlineStr">
+        <is>
+          <t>2022-01 ~ 2024-01</t>
+        </is>
+      </c>
+      <c r="E667" t="inlineStr">
+        <is>
+          <t>0583</t>
+        </is>
+      </c>
+      <c r="F667" t="inlineStr">
+        <is>
+          <t>ANO</t>
+        </is>
+      </c>
+      <c r="G667" t="inlineStr">
+        <is>
+          <t>06/2019 - 02/2024</t>
+        </is>
+      </c>
+      <c r="H667" t="inlineStr">
+        <is>
+          <t>RDE047 + RDV021 | 45.142.000, RDE047 + RDV026 | 73.907.047</t>
+        </is>
+      </c>
+      <c r="I667" t="inlineStr">
+        <is>
+          <t>BH SENS</t>
+        </is>
+      </c>
+      <c r="J667" t="inlineStr">
+        <is>
+          <t>433</t>
+        </is>
+      </c>
+    </row>
+    <row r="668">
+      <c r="A668" t="inlineStr">
+        <is>
+          <t>PORSCHE</t>
+        </is>
+      </c>
+      <c r="B668" t="inlineStr">
+        <is>
+          <t>Taycan Sport Turismo</t>
+        </is>
+      </c>
+      <c r="C668" t="inlineStr">
+        <is>
+          <t>4S Performancebatterie</t>
+        </is>
+      </c>
+      <c r="D668" t="inlineStr">
+        <is>
+          <t>2024-01 ~ 至今</t>
+        </is>
+      </c>
+      <c r="E668" t="inlineStr">
+        <is>
+          <t>0583</t>
+        </is>
+      </c>
+      <c r="F668" t="inlineStr">
+        <is>
+          <t>AOW</t>
+        </is>
+      </c>
+      <c r="G668" t="inlineStr">
+        <is>
+          <t>03/2024 -, 06/2019 - 02/2024</t>
+        </is>
+      </c>
+      <c r="H668" t="inlineStr">
+        <is>
+          <t>RDE047 + RDV021 | 45.142.000, RDE047 + RDV026 | 73.907.047, RDE254+RDV021, RDE254+RDV026</t>
+        </is>
+      </c>
+      <c r="I668" t="inlineStr">
+        <is>
+          <t>BH SENS</t>
+        </is>
+      </c>
+      <c r="J668" t="inlineStr">
+        <is>
+          <t>433</t>
+        </is>
+      </c>
+    </row>
+    <row r="669">
+      <c r="A669" t="inlineStr">
+        <is>
+          <t>PORSCHE</t>
+        </is>
+      </c>
+      <c r="B669" t="inlineStr">
+        <is>
+          <t>Taycan Sport Turismo</t>
+        </is>
+      </c>
+      <c r="C669" t="inlineStr">
+        <is>
+          <t>4S Performancebatterie Plus</t>
+        </is>
+      </c>
+      <c r="D669" t="inlineStr">
+        <is>
+          <t>2024-01 ~ 至今</t>
+        </is>
+      </c>
+      <c r="E669" t="inlineStr">
+        <is>
+          <t>0583</t>
+        </is>
+      </c>
+      <c r="F669" t="inlineStr">
+        <is>
+          <t>AOV</t>
+        </is>
+      </c>
+      <c r="G669" t="inlineStr">
+        <is>
+          <t>03/2024 -, 06/2019 - 02/2024</t>
+        </is>
+      </c>
+      <c r="H669" t="inlineStr">
+        <is>
+          <t>RDE047 + RDV021 | 45.142.000, RDE047 + RDV026 | 73.907.047, RDE254+RDV021, RDE254+RDV026</t>
+        </is>
+      </c>
+      <c r="I669" t="inlineStr">
+        <is>
+          <t>BH SENS</t>
+        </is>
+      </c>
+      <c r="J669" t="inlineStr">
+        <is>
+          <t>433</t>
+        </is>
+      </c>
+    </row>
+    <row r="670">
+      <c r="A670" t="inlineStr">
+        <is>
+          <t>PORSCHE</t>
+        </is>
+      </c>
+      <c r="B670" t="inlineStr">
+        <is>
+          <t>Taycan Sport Turismo</t>
+        </is>
+      </c>
+      <c r="C670" t="inlineStr">
+        <is>
+          <t>GTS</t>
+        </is>
+      </c>
+      <c r="D670" t="inlineStr">
+        <is>
+          <t>2022-01 ~ 2024-01</t>
+        </is>
+      </c>
+      <c r="E670" t="inlineStr">
+        <is>
+          <t>0583</t>
+        </is>
+      </c>
+      <c r="F670" t="inlineStr">
+        <is>
+          <t>ANH</t>
+        </is>
+      </c>
+      <c r="G670" t="inlineStr">
+        <is>
+          <t>06/2019 - 02/2024</t>
+        </is>
+      </c>
+      <c r="H670" t="inlineStr">
+        <is>
+          <t>RDE047 + RDV021 | 45.142.000, RDE047 + RDV026 | 73.907.047</t>
+        </is>
+      </c>
+      <c r="I670" t="inlineStr">
+        <is>
+          <t>BH SENS</t>
+        </is>
+      </c>
+      <c r="J670" t="inlineStr">
+        <is>
+          <t>433</t>
+        </is>
+      </c>
+    </row>
+    <row r="671">
+      <c r="A671" t="inlineStr">
+        <is>
+          <t>PORSCHE</t>
+        </is>
+      </c>
+      <c r="B671" t="inlineStr">
+        <is>
+          <t>Taycan Sport Turismo</t>
+        </is>
+      </c>
+      <c r="C671" t="inlineStr">
+        <is>
+          <t>GTS Performancebatterie Plus</t>
+        </is>
+      </c>
+      <c r="D671" t="inlineStr">
+        <is>
+          <t>2024-01 ~ 至今</t>
+        </is>
+      </c>
+      <c r="E671" t="inlineStr">
+        <is>
+          <t>0583</t>
+        </is>
+      </c>
+      <c r="F671" t="inlineStr">
+        <is>
+          <t>APJ</t>
+        </is>
+      </c>
+      <c r="G671" t="inlineStr">
+        <is>
+          <t>03/2024 -, 06/2019 - 02/2024</t>
+        </is>
+      </c>
+      <c r="H671" t="inlineStr">
+        <is>
+          <t>RDE047 + RDV021 | 45.142.000, RDE047 + RDV026 | 73.907.047, RDE254+RDV021, RDE254+RDV026</t>
+        </is>
+      </c>
+      <c r="I671" t="inlineStr">
+        <is>
+          <t>BH SENS</t>
+        </is>
+      </c>
+      <c r="J671" t="inlineStr">
+        <is>
+          <t>433</t>
+        </is>
+      </c>
+    </row>
+    <row r="672">
+      <c r="A672" t="inlineStr">
+        <is>
+          <t>PORSCHE</t>
+        </is>
+      </c>
+      <c r="B672" t="inlineStr">
+        <is>
+          <t>Taycan Sport Turismo</t>
+        </is>
+      </c>
+      <c r="C672" t="inlineStr">
+        <is>
+          <t>Performancebatterie</t>
+        </is>
+      </c>
+      <c r="D672" t="inlineStr">
+        <is>
+          <t>2024-01 ~ 至今</t>
+        </is>
+      </c>
+      <c r="E672" t="inlineStr">
+        <is>
+          <t>0583</t>
+        </is>
+      </c>
+      <c r="F672" t="inlineStr">
+        <is>
+          <t>APA</t>
+        </is>
+      </c>
+      <c r="G672" t="inlineStr">
+        <is>
+          <t>03/2024 -, 06/2019 - 02/2024</t>
+        </is>
+      </c>
+      <c r="H672" t="inlineStr">
+        <is>
+          <t>RDE047 + RDV021 | 45.142.000, RDE047 + RDV026 | 73.907.047, RDE254+RDV021, RDE254+RDV026</t>
+        </is>
+      </c>
+      <c r="I672" t="inlineStr">
+        <is>
+          <t>BH SENS</t>
+        </is>
+      </c>
+      <c r="J672" t="inlineStr">
+        <is>
+          <t>433</t>
+        </is>
+      </c>
+    </row>
+    <row r="673">
+      <c r="A673" t="inlineStr">
+        <is>
+          <t>PORSCHE</t>
+        </is>
+      </c>
+      <c r="B673" t="inlineStr">
+        <is>
+          <t>Taycan Sport Turismo</t>
+        </is>
+      </c>
+      <c r="C673" t="inlineStr">
+        <is>
+          <t>Performancebatterie Plus</t>
+        </is>
+      </c>
+      <c r="D673" t="inlineStr">
+        <is>
+          <t>2024-01 ~ 至今</t>
+        </is>
+      </c>
+      <c r="E673" t="inlineStr">
+        <is>
+          <t>0583</t>
+        </is>
+      </c>
+      <c r="F673" t="inlineStr">
+        <is>
+          <t>AOZ</t>
+        </is>
+      </c>
+      <c r="G673" t="inlineStr">
+        <is>
+          <t>03/2024 -, 06/2019 - 02/2024</t>
+        </is>
+      </c>
+      <c r="H673" t="inlineStr">
+        <is>
+          <t>RDE047 + RDV021 | 45.142.000, RDE047 + RDV026 | 73.907.047, RDE254+RDV021, RDE254+RDV026</t>
+        </is>
+      </c>
+      <c r="I673" t="inlineStr">
+        <is>
+          <t>BH SENS</t>
+        </is>
+      </c>
+      <c r="J673" t="inlineStr">
+        <is>
+          <t>433</t>
+        </is>
+      </c>
+    </row>
+    <row r="674">
+      <c r="A674" t="inlineStr">
+        <is>
+          <t>PORSCHE</t>
+        </is>
+      </c>
+      <c r="B674" t="inlineStr">
+        <is>
+          <t>Taycan Sport Turismo</t>
+        </is>
+      </c>
+      <c r="C674" t="inlineStr">
+        <is>
+          <t>Turbo</t>
+        </is>
+      </c>
+      <c r="D674" t="inlineStr">
+        <is>
+          <t>2021-01 ~ 2024-01</t>
+        </is>
+      </c>
+      <c r="E674" t="inlineStr">
+        <is>
+          <t>0583</t>
+        </is>
+      </c>
+      <c r="F674" t="inlineStr">
+        <is>
+          <t>ANH</t>
+        </is>
+      </c>
+      <c r="G674" t="inlineStr">
+        <is>
+          <t>06/2019 - 02/2024</t>
+        </is>
+      </c>
+      <c r="H674" t="inlineStr">
+        <is>
+          <t>RDE047 + RDV021 | 45.142.000, RDE047 + RDV026 | 73.907.047</t>
+        </is>
+      </c>
+      <c r="I674" t="inlineStr">
+        <is>
+          <t>BH SENS</t>
+        </is>
+      </c>
+      <c r="J674" t="inlineStr">
+        <is>
+          <t>433</t>
+        </is>
+      </c>
+    </row>
+    <row r="675">
+      <c r="A675" t="inlineStr">
+        <is>
+          <t>PORSCHE</t>
+        </is>
+      </c>
+      <c r="B675" t="inlineStr">
+        <is>
+          <t>Taycan Sport Turismo</t>
+        </is>
+      </c>
+      <c r="C675" t="inlineStr">
+        <is>
+          <t>Turbo Performancebatterie Plus</t>
+        </is>
+      </c>
+      <c r="D675" t="inlineStr">
+        <is>
+          <t>2024-01 ~ 至今</t>
+        </is>
+      </c>
+      <c r="E675" t="inlineStr">
+        <is>
+          <t>0583</t>
+        </is>
+      </c>
+      <c r="F675" t="inlineStr">
+        <is>
+          <t>AOU</t>
+        </is>
+      </c>
+      <c r="G675" t="inlineStr">
+        <is>
+          <t>03/2024 -, 06/2019 - 02/2024</t>
+        </is>
+      </c>
+      <c r="H675" t="inlineStr">
+        <is>
+          <t>RDE047 + RDV021 | 45.142.000, RDE047 + RDV026 | 73.907.047, RDE254+RDV021, RDE254+RDV026</t>
+        </is>
+      </c>
+      <c r="I675" t="inlineStr">
+        <is>
+          <t>BH SENS</t>
+        </is>
+      </c>
+      <c r="J675" t="inlineStr">
+        <is>
+          <t>433</t>
+        </is>
+      </c>
+    </row>
+    <row r="676">
+      <c r="A676" t="inlineStr">
+        <is>
+          <t>PORSCHE</t>
+        </is>
+      </c>
+      <c r="B676" t="inlineStr">
+        <is>
+          <t>Taycan Sport Turismo</t>
+        </is>
+      </c>
+      <c r="C676" t="inlineStr">
+        <is>
+          <t>Turbo S</t>
+        </is>
+      </c>
+      <c r="D676" t="inlineStr">
+        <is>
+          <t>2021-01 ~ 2024-01</t>
+        </is>
+      </c>
+      <c r="E676" t="inlineStr">
+        <is>
+          <t>0583</t>
+        </is>
+      </c>
+      <c r="F676" t="inlineStr">
+        <is>
+          <t>ANH</t>
+        </is>
+      </c>
+      <c r="G676" t="inlineStr">
+        <is>
+          <t>06/2019 - 02/2024</t>
+        </is>
+      </c>
+      <c r="H676" t="inlineStr">
+        <is>
+          <t>RDE047 + RDV021 | 45.142.000, RDE047 + RDV026 | 73.907.047</t>
+        </is>
+      </c>
+      <c r="I676" t="inlineStr">
+        <is>
+          <t>BH SENS</t>
+        </is>
+      </c>
+      <c r="J676" t="inlineStr">
+        <is>
+          <t>433</t>
+        </is>
+      </c>
+    </row>
+    <row r="677">
+      <c r="A677" t="inlineStr">
+        <is>
+          <t>PORSCHE</t>
+        </is>
+      </c>
+      <c r="B677" t="inlineStr">
+        <is>
+          <t>Taycan Sport Turismo</t>
+        </is>
+      </c>
+      <c r="C677" t="inlineStr">
+        <is>
+          <t>Turbo S Performancebatterie Plus</t>
+        </is>
+      </c>
+      <c r="D677" t="inlineStr">
+        <is>
+          <t>2024-01 ~ 至今</t>
+        </is>
+      </c>
+      <c r="E677" t="inlineStr">
+        <is>
+          <t>0583</t>
+        </is>
+      </c>
+      <c r="F677" t="inlineStr">
+        <is>
+          <t>AOT</t>
+        </is>
+      </c>
+      <c r="G677" t="inlineStr">
+        <is>
+          <t>03/2024 -, 06/2019 - 02/2024</t>
+        </is>
+      </c>
+      <c r="H677" t="inlineStr">
+        <is>
+          <t>RDE047 + RDV021 | 45.142.000, RDE047 + RDV026 | 73.907.047, RDE254+RDV021, RDE254+RDV026</t>
+        </is>
+      </c>
+      <c r="I677" t="inlineStr">
+        <is>
+          <t>BH SENS</t>
+        </is>
+      </c>
+      <c r="J677" t="inlineStr">
+        <is>
+          <t>433</t>
+        </is>
+      </c>
+    </row>
+    <row r="678">
+      <c r="A678" t="inlineStr">
+        <is>
+          <t>PORSCHE</t>
+        </is>
+      </c>
+      <c r="B678" t="inlineStr">
+        <is>
+          <t>Taycan Sport Turismo</t>
+        </is>
+      </c>
+      <c r="C678" t="inlineStr">
+        <is>
+          <t>electric</t>
+        </is>
+      </c>
+      <c r="D678" t="inlineStr">
+        <is>
+          <t>2022-01 ~ 2024-01</t>
+        </is>
+      </c>
+      <c r="E678" t="inlineStr">
+        <is>
+          <t>0583</t>
+        </is>
+      </c>
+      <c r="F678" t="inlineStr">
+        <is>
+          <t>ANN</t>
+        </is>
+      </c>
+      <c r="G678" t="inlineStr">
+        <is>
+          <t>06/2019 - 02/2024</t>
+        </is>
+      </c>
+      <c r="H678" t="inlineStr">
+        <is>
+          <t>RDE047 + RDV021 | 45.142.000, RDE047 + RDV026 | 73.907.047</t>
+        </is>
+      </c>
+      <c r="I678" t="inlineStr">
+        <is>
+          <t>BH SENS</t>
+        </is>
+      </c>
+      <c r="J678" t="inlineStr">
         <is>
           <t>433</t>
         </is>
